--- a/colombres/Agosto/AGOSTO COLOMBRES 360.xlsx
+++ b/colombres/Agosto/AGOSTO COLOMBRES 360.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\JULIO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\colombres\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D811B4C-EDEF-4A76-BD11-BE3973EFDCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3EF8E34-7847-4275-987D-B55007368366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$121</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$125</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="181">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -420,18 +420,12 @@
 Nº de cuenta: 04097978-001</t>
   </si>
   <si>
-    <t>VTO 14/08</t>
-  </si>
-  <si>
     <t xml:space="preserve">METROGAS - Cliente 30008873781 </t>
   </si>
   <si>
     <t>Ortega Daniel O. - CUIT 20-22388558-7 - Servicio - Fumigación</t>
   </si>
   <si>
-    <t xml:space="preserve">Ascensores Premec - Mantenimiento junio 2025 </t>
-  </si>
-  <si>
     <t>G Group - Ramón Falcón 395, Lomas de Zamora - CUIT 33-71473408-9  - Service grupo electrógeno</t>
   </si>
   <si>
@@ -507,9 +501,6 @@
     <t>Transf 08/07</t>
   </si>
   <si>
-    <t>Sasa - Servicio de confeccion y liquidacion de datos - Junio 2025 - Administracion anterior</t>
-  </si>
-  <si>
     <t>Transf 07/07</t>
   </si>
   <si>
@@ -562,6 +553,30 @@
   </si>
   <si>
     <t>EL DEPOSITO DEL MES PASADO DE 545.000 ES DE EL</t>
+  </si>
+  <si>
+    <t>VTO 15/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascensores Premec - Mantenimiento JULIO 2025 </t>
+  </si>
+  <si>
+    <t>Sasa - Servicio de confeccion y liquidacion de datos - JULIO 2025 - Administracion anterior</t>
+  </si>
+  <si>
+    <t>Librería - papelera</t>
+  </si>
+  <si>
+    <t>FAGUAR - Uniforme porteria - CUIT 00-02381237-3</t>
+  </si>
+  <si>
+    <t>Transf 20/08</t>
+  </si>
+  <si>
+    <t>Fotocopias</t>
+  </si>
+  <si>
+    <t>Ascensores Premec - Reparacion y reinstalacion de indicador de posicion según preupuesto aprobado</t>
   </si>
 </sst>
 </file>
@@ -569,12 +584,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -1179,10 +1194,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1190,14 +1205,14 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1205,7 +1220,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1213,44 +1228,44 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="19" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1264,68 +1279,68 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
@@ -1337,14 +1352,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1358,8 +1373,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1370,19 +1385,62 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1404,41 +1462,23 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1452,9 +1492,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1464,9 +1501,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1482,19 +1516,8 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1849,20 +1872,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L125"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L129"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="136" t="s">
         <v>124</v>
       </c>
@@ -1870,7 +1893,7 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="129" t="s">
         <v>126</v>
       </c>
@@ -1878,7 +1901,7 @@
       <c r="C2" s="129"/>
       <c r="D2" s="129"/>
     </row>
-    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="129" t="s">
         <v>125</v>
       </c>
@@ -1886,76 +1909,76 @@
       <c r="C3" s="129"/>
       <c r="D3" s="129"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="156" t="s">
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="158" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="156"/>
+      <c r="B4" s="158"/>
       <c r="C4" s="130"/>
       <c r="D4" s="130"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="156"/>
-      <c r="B5" s="156"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="158"/>
+      <c r="B5" s="158"/>
       <c r="C5" s="130"/>
       <c r="D5" s="130"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="156"/>
-      <c r="B6" s="156"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="158"/>
+      <c r="B6" s="158"/>
       <c r="C6" s="130"/>
       <c r="D6" s="130"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="156"/>
-      <c r="B7" s="156"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="158"/>
+      <c r="B7" s="158"/>
       <c r="C7" s="130"/>
       <c r="D7" s="130"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="153" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="153"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="153"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="152" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="157" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="157"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="157"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="167" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="152"/>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="152"/>
-      <c r="B15" s="152"/>
-      <c r="C15" s="152"/>
-      <c r="D15" s="152"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="152"/>
-      <c r="B16" s="152"/>
-      <c r="C16" s="152"/>
-      <c r="D16" s="152"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="152"/>
-      <c r="B17" s="152"/>
-      <c r="C17" s="152"/>
-      <c r="D17" s="152"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="167"/>
+      <c r="C14" s="167"/>
+      <c r="D14" s="167"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="167"/>
+      <c r="B15" s="167"/>
+      <c r="C15" s="167"/>
+      <c r="D15" s="167"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="167"/>
+      <c r="B16" s="167"/>
+      <c r="C16" s="167"/>
+      <c r="D16" s="167"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="167"/>
+      <c r="B17" s="167"/>
+      <c r="C17" s="167"/>
+      <c r="D17" s="167"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -1963,7 +1986,7 @@
       <c r="C21" s="9"/>
       <c r="D21" s="13"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="s">
         <v>80</v>
       </c>
@@ -1971,9 +1994,9 @@
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="122">
@@ -1981,7 +2004,7 @@
       </c>
       <c r="D23" s="84"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>84</v>
       </c>
@@ -1991,7 +2014,7 @@
       </c>
       <c r="D24" s="84"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
@@ -2000,9 +2023,9 @@
       <c r="D25" s="84"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="122">
@@ -2011,7 +2034,7 @@
       <c r="D26" s="84"/>
       <c r="G26" s="14"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="50" t="s">
         <v>82</v>
       </c>
@@ -2023,9 +2046,9 @@
       <c r="D27" s="85"/>
       <c r="G27" s="124"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="135" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="122">
@@ -2034,7 +2057,7 @@
       <c r="D28" s="84"/>
       <c r="G28" s="124"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>81</v>
       </c>
@@ -2045,7 +2068,7 @@
       <c r="D29" s="84"/>
       <c r="G29" s="14"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
@@ -2054,9 +2077,9 @@
       <c r="D30" s="84"/>
       <c r="G30" s="14"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="118">
@@ -2065,7 +2088,7 @@
       <c r="D31" s="84"/>
       <c r="G31" s="14"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="50" t="s">
         <v>82</v>
       </c>
@@ -2076,9 +2099,9 @@
       </c>
       <c r="D32" s="85"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="122">
@@ -2086,7 +2109,7 @@
       </c>
       <c r="D33" s="134"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>81</v>
       </c>
@@ -2096,7 +2119,7 @@
       </c>
       <c r="D34" s="134"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>83</v>
       </c>
@@ -2104,9 +2127,9 @@
       <c r="C35" s="122"/>
       <c r="D35" s="134"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="118">
@@ -2114,7 +2137,7 @@
       </c>
       <c r="D36" s="134"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="50" t="s">
         <v>82</v>
       </c>
@@ -2125,7 +2148,7 @@
       </c>
       <c r="D37" s="85"/>
     </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="18" t="s">
         <v>0</v>
       </c>
@@ -2138,7 +2161,7 @@
       <c r="E38" s="14"/>
       <c r="F38" s="14"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="27" t="s">
         <v>38</v>
       </c>
@@ -2147,7 +2170,7 @@
       <c r="D39" s="87"/>
       <c r="F39" s="14"/>
     </row>
-    <row r="40" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="59" t="s">
         <v>39</v>
       </c>
@@ -2156,31 +2179,31 @@
       <c r="D40" s="88"/>
       <c r="G40" s="14"/>
     </row>
-    <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="137" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B41" s="127"/>
       <c r="C41" s="122"/>
       <c r="D41" s="88"/>
       <c r="G41" s="14"/>
     </row>
-    <row r="42" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="137" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B42" s="127"/>
       <c r="C42" s="122">
         <v>392500</v>
       </c>
       <c r="D42" s="141" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G42" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="18" t="s">
         <v>34</v>
       </c>
@@ -2191,7 +2214,7 @@
         <v>392500</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="25" t="s">
         <v>77</v>
       </c>
@@ -2199,31 +2222,31 @@
       <c r="C44" s="29"/>
       <c r="D44" s="61"/>
     </row>
-    <row r="45" spans="1:7" s="35" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="154" t="s">
-        <v>136</v>
-      </c>
-      <c r="B45" s="155"/>
+    <row r="45" spans="1:7" s="35" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="155" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" s="156"/>
       <c r="C45" s="144">
         <v>175052</v>
       </c>
       <c r="D45" s="112" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="154" t="s">
-        <v>137</v>
-      </c>
-      <c r="B46" s="155"/>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="155" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="156"/>
       <c r="C46" s="145">
         <v>4203</v>
       </c>
       <c r="D46" s="112" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="18" t="s">
         <v>1</v>
       </c>
@@ -2234,7 +2257,7 @@
         <v>179255</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="27" t="s">
         <v>35</v>
       </c>
@@ -2242,58 +2265,58 @@
       <c r="C48" s="33"/>
       <c r="D48" s="91"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="187">
+        <v>1494923.37</v>
+      </c>
+      <c r="D49" s="119" t="s">
+        <v>148</v>
+      </c>
+      <c r="F49" s="138"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="186">
+        <v>17314.93</v>
+      </c>
+      <c r="D50" s="119" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="31">
-        <v>2530143.65</v>
-      </c>
-      <c r="D49" s="119" t="s">
-        <v>150</v>
-      </c>
-      <c r="F49" s="138"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="111">
-        <v>29588.720000000001</v>
-      </c>
-      <c r="D50" s="119" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>144</v>
-      </c>
       <c r="B51" s="5"/>
-      <c r="C51" s="111">
-        <v>266298.44</v>
+      <c r="C51" s="186">
+        <v>155834.29999999999</v>
       </c>
       <c r="D51" s="119" t="str">
         <f>D50</f>
         <v>Debito 14/07</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B52" s="5"/>
-      <c r="C52" s="111">
-        <v>493841.29</v>
+      <c r="C52" s="186">
+        <v>299113.43</v>
       </c>
       <c r="D52" s="120" t="str">
         <f>D51</f>
         <v>Debito 14/07</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="18" t="s">
         <v>2</v>
       </c>
@@ -2301,10 +2324,10 @@
       <c r="C53" s="34"/>
       <c r="D53" s="90">
         <f>SUM(C49:C52)</f>
-        <v>3319872.1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1967186.03</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="27" t="s">
         <v>37</v>
       </c>
@@ -2312,551 +2335,601 @@
       <c r="C54" s="33"/>
       <c r="D54" s="91"/>
     </row>
-    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" s="5"/>
+      <c r="C55" s="186">
+        <v>519920.12</v>
+      </c>
+      <c r="D55" s="96" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="186">
+        <v>50410.45</v>
+      </c>
+      <c r="D56" s="120" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="111">
-        <v>529265.89</v>
-      </c>
-      <c r="D55" s="96" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
+      <c r="B57" s="5"/>
+      <c r="C57" s="186">
+        <v>713548.29</v>
+      </c>
+      <c r="D57" s="96" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="155" t="s">
+        <v>180</v>
+      </c>
+      <c r="B58" s="156"/>
+      <c r="C58" s="186">
+        <v>308630</v>
+      </c>
+      <c r="D58" s="132" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="161" t="s">
+        <v>174</v>
+      </c>
+      <c r="B59" s="162"/>
+      <c r="C59" s="186">
+        <v>158501</v>
+      </c>
+      <c r="D59" s="132" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="111">
-        <v>54600.160000000003</v>
-      </c>
-      <c r="D56" s="120" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="111">
-        <v>727695.66</v>
-      </c>
-      <c r="D57" s="96" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="146" t="s">
-        <v>131</v>
-      </c>
-      <c r="B58" s="147"/>
-      <c r="C58" s="111"/>
-      <c r="D58" s="96"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B59" s="126"/>
-      <c r="C59" s="111"/>
-      <c r="D59" s="96"/>
-    </row>
-    <row r="60" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="18" t="s">
+      <c r="B60" s="126"/>
+      <c r="C60" s="111"/>
+      <c r="D60" s="96"/>
+    </row>
+    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="18" t="s">
         <v>3</v>
-      </c>
-      <c r="B60" s="18"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="90">
-        <f>SUM(C55:C59)</f>
-        <v>1311561.71</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="27" t="s">
-        <v>36</v>
       </c>
       <c r="B61" s="18"/>
       <c r="C61" s="32"/>
-      <c r="D61" s="94"/>
-    </row>
-    <row r="62" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="148" t="s">
+      <c r="D61" s="90">
+        <f>SUM(C55:C60)</f>
+        <v>1751009.8599999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="18"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="94"/>
+    </row>
+    <row r="63" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="163" t="s">
+        <v>130</v>
+      </c>
+      <c r="B63" s="164"/>
+      <c r="C63" s="111"/>
+      <c r="D63" s="115"/>
+    </row>
+    <row r="64" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="146" t="s">
+        <v>176</v>
+      </c>
+      <c r="B64" s="147"/>
+      <c r="C64" s="186">
+        <v>11000</v>
+      </c>
+      <c r="D64" s="115"/>
+    </row>
+    <row r="65" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="146" t="s">
+        <v>179</v>
+      </c>
+      <c r="B65" s="147"/>
+      <c r="C65" s="186">
+        <v>48000</v>
+      </c>
+      <c r="D65" s="115"/>
+    </row>
+    <row r="66" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="163" t="s">
+        <v>131</v>
+      </c>
+      <c r="B66" s="164"/>
+      <c r="C66" s="111"/>
+      <c r="D66" s="114"/>
+    </row>
+    <row r="67" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="165" t="s">
         <v>132</v>
       </c>
-      <c r="B62" s="149"/>
-      <c r="C62" s="111"/>
-      <c r="D62" s="115"/>
-    </row>
-    <row r="63" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="148" t="s">
+      <c r="B67" s="166"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="93"/>
+    </row>
+    <row r="68" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="159" t="s">
+        <v>152</v>
+      </c>
+      <c r="B68" s="160"/>
+      <c r="C68" s="31">
+        <v>250000</v>
+      </c>
+      <c r="D68" s="132" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="159" t="s">
+        <v>177</v>
+      </c>
+      <c r="B69" s="160"/>
+      <c r="C69" s="187">
+        <v>99268</v>
+      </c>
+      <c r="D69" s="132" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="159" t="s">
+        <v>175</v>
+      </c>
+      <c r="B70" s="160"/>
+      <c r="C70" s="31">
+        <v>33429</v>
+      </c>
+      <c r="D70" s="132" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="159" t="s">
+        <v>156</v>
+      </c>
+      <c r="B71" s="160"/>
+      <c r="C71" s="31">
+        <v>70000</v>
+      </c>
+      <c r="D71" s="132" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="159" t="s">
+        <v>153</v>
+      </c>
+      <c r="B72" s="160"/>
+      <c r="C72" s="31">
+        <v>191330</v>
+      </c>
+      <c r="D72" s="132" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="27"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="98">
+        <f>SUM(C63:C67)</f>
+        <v>59000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B74" s="60"/>
+      <c r="C74" s="20"/>
+      <c r="D74" s="94"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B75" s="5"/>
+      <c r="C75" s="111">
+        <v>56820.35</v>
+      </c>
+      <c r="D75" s="99"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B63" s="149"/>
-      <c r="C63" s="111"/>
-      <c r="D63" s="114"/>
-    </row>
-    <row r="64" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="150" t="s">
-        <v>134</v>
-      </c>
-      <c r="B64" s="151"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="93"/>
-    </row>
-    <row r="65" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="157" t="s">
-        <v>154</v>
-      </c>
-      <c r="B65" s="158"/>
-      <c r="C65" s="31">
-        <v>250000</v>
-      </c>
-      <c r="D65" s="132" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="157" t="s">
-        <v>157</v>
-      </c>
-      <c r="B66" s="158"/>
-      <c r="C66" s="31">
-        <v>33429</v>
-      </c>
-      <c r="D66" s="132" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="157" t="s">
-        <v>159</v>
-      </c>
-      <c r="B67" s="158"/>
-      <c r="C67" s="31">
-        <v>70000</v>
-      </c>
-      <c r="D67" s="132" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="157" t="s">
-        <v>155</v>
-      </c>
-      <c r="B68" s="158"/>
-      <c r="C68" s="31">
-        <v>191330</v>
-      </c>
-      <c r="D68" s="132" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B69" s="27"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="98">
-        <f>SUM(C62:C64)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B70" s="60"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="94"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B71" s="5"/>
-      <c r="C71" s="111">
-        <v>56820.35</v>
-      </c>
-      <c r="D71" s="99"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="111">
+      <c r="B76" s="5"/>
+      <c r="C76" s="111">
         <v>142713.93</v>
       </c>
-      <c r="D72" s="97"/>
-    </row>
-    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="46" t="s">
+      <c r="D76" s="97"/>
+    </row>
+    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B73" s="46"/>
-      <c r="C73" s="100"/>
-      <c r="D73" s="90">
-        <f>SUM(C71:C72)</f>
+      <c r="B77" s="46"/>
+      <c r="C77" s="100"/>
+      <c r="D77" s="90">
+        <f>SUM(C75:C76)</f>
         <v>199534.28</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="84"/>
-      <c r="D74" s="101"/>
-    </row>
-    <row r="75" spans="1:6" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="159" t="s">
-        <v>174</v>
-      </c>
-      <c r="B75" s="160"/>
-      <c r="C75" s="161"/>
-      <c r="D75" s="102">
+    <row r="78" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="5"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="84"/>
+      <c r="D78" s="101"/>
+    </row>
+    <row r="79" spans="1:5" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="149" t="s">
+        <v>171</v>
+      </c>
+      <c r="B79" s="150"/>
+      <c r="C79" s="151"/>
+      <c r="D79" s="102">
         <v>2334921.91</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="1"/>
-      <c r="C76" s="103"/>
-      <c r="D76" s="104"/>
-      <c r="E76" s="41"/>
-    </row>
-    <row r="77" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
+    <row r="80" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="1"/>
+      <c r="C80" s="103"/>
+      <c r="D80" s="104"/>
+      <c r="E80" s="41"/>
+    </row>
+    <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B77" s="10"/>
-      <c r="C77" s="105"/>
-      <c r="D77" s="106">
-        <f>(SUM(D29:D75))</f>
-        <v>11999999.999999998</v>
-      </c>
-      <c r="E77" s="41"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C78" s="103"/>
-      <c r="D78" s="103"/>
-      <c r="F78" s="143"/>
-    </row>
-    <row r="79" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C79" s="103"/>
-      <c r="D79" s="103"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="11" t="s">
+      <c r="B81" s="10"/>
+      <c r="C81" s="105"/>
+      <c r="D81" s="106">
+        <f>(SUM(D29:D79))</f>
+        <v>11145762.08</v>
+      </c>
+      <c r="E81" s="41"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C82" s="103"/>
+      <c r="D82" s="103"/>
+      <c r="F82" s="143"/>
+    </row>
+    <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C83" s="103"/>
+      <c r="D83" s="103"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B80" s="12"/>
-      <c r="C80" s="107"/>
-      <c r="D80" s="108"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="154"/>
-      <c r="B81" s="155"/>
-      <c r="C81" s="95"/>
-      <c r="D81" s="92"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="154"/>
-      <c r="B82" s="155"/>
-      <c r="C82" s="95"/>
-      <c r="D82" s="92"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="116"/>
-      <c r="B83" s="117"/>
-      <c r="C83" s="95"/>
-      <c r="D83" s="92"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="44"/>
-      <c r="B84" s="43"/>
-      <c r="C84" s="52"/>
-      <c r="D84" s="52">
-        <f>SUM(C81:C83)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="21" t="s">
+      <c r="B84" s="12"/>
+      <c r="C84" s="107"/>
+      <c r="D84" s="108"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="155"/>
+      <c r="B85" s="156"/>
+      <c r="C85" s="95"/>
+      <c r="D85" s="92"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="155"/>
+      <c r="B86" s="156"/>
+      <c r="C86" s="95"/>
+      <c r="D86" s="92"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="116"/>
+      <c r="B87" s="117"/>
+      <c r="C87" s="95"/>
+      <c r="D87" s="92"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="44"/>
+      <c r="B88" s="43"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52">
+        <f>SUM(C85:C87)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B87" s="21"/>
-      <c r="C87" s="22"/>
-      <c r="D87" s="125"/>
-    </row>
-    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
+      <c r="B91" s="21"/>
+      <c r="C91" s="22"/>
+      <c r="D91" s="125"/>
+    </row>
+    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="93" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B89" s="10"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="62">
-        <f>D84+D87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="82" t="s">
+      <c r="B93" s="10"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="62">
+        <f>D88+D91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="95" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="B91" s="83">
-        <f>D77</f>
-        <v>11999999.999999998</v>
-      </c>
-      <c r="C91" s="41"/>
-    </row>
-    <row r="92" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="82" t="s">
+      <c r="B95" s="83">
+        <f>D81</f>
+        <v>11145762.08</v>
+      </c>
+      <c r="C95" s="41"/>
+    </row>
+    <row r="96" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="B92" s="83">
-        <f>D77-D75</f>
-        <v>9665078.089999998</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="82" t="s">
+      <c r="B96" s="83">
+        <f>D81-D79</f>
+        <v>8810840.1699999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="B93" s="83">
-        <f>D89-D87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="82" t="s">
+      <c r="B97" s="83">
+        <f>D93-D91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="B94" s="83">
-        <f>D89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="164"/>
-      <c r="B97" s="164"/>
-      <c r="C97" s="164"/>
-      <c r="D97" s="164"/>
-    </row>
-    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="164"/>
-      <c r="B98" s="164"/>
-      <c r="C98" s="164"/>
-      <c r="D98" s="164"/>
-    </row>
-    <row r="99" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="164"/>
-      <c r="B99" s="164"/>
-      <c r="C99" s="164"/>
-      <c r="D99" s="164"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="15" t="s">
+      <c r="B98" s="83">
+        <f>D93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="154"/>
+      <c r="B101" s="154"/>
+      <c r="C101" s="154"/>
+      <c r="D101" s="154"/>
+    </row>
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="154"/>
+      <c r="B102" s="154"/>
+      <c r="C102" s="154"/>
+      <c r="D102" s="154"/>
+    </row>
+    <row r="103" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="154"/>
+      <c r="B103" s="154"/>
+      <c r="C103" s="154"/>
+      <c r="D103" s="154"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B101" s="37"/>
-    </row>
-    <row r="102" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="24" t="s">
+      <c r="B105" s="37"/>
+    </row>
+    <row r="106" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B102" s="121">
+      <c r="B106" s="121">
         <v>-847927.83</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="16" t="s">
+    <row r="107" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B103" s="38">
+      <c r="B107" s="38">
         <f>PRORRATEO!H34</f>
         <v>9758198.1199999992</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="16" t="s">
+    <row r="108" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B104" s="97">
-        <f>B120</f>
+      <c r="B108" s="97">
+        <f>B124</f>
         <v>2145810</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="B105" s="97">
+    <row r="109" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B109" s="97">
         <v>-1650000</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="B106" s="97">
+    <row r="110" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B110" s="97">
         <v>-39552</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="36" t="s">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B107" s="97">
-        <f>-B92</f>
-        <v>-9665078.089999998</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="17" t="s">
+      <c r="B111" s="97">
+        <f>-B96</f>
+        <v>-8810840.1699999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B108" s="97">
-        <f>-(B93)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="23" t="s">
+      <c r="B112" s="97">
+        <f>-(B97)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A113" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B109" s="121">
-        <f>SUM(B102:B108)</f>
-        <v>-298549.79999999888</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="39"/>
-      <c r="C110" s="41"/>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="163" t="s">
+      <c r="B113" s="121">
+        <f>SUM(B106:B112)</f>
+        <v>555688.11999999918</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B114" s="39"/>
+      <c r="C114" s="41"/>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A116" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="B112" s="163"/>
-    </row>
-    <row r="113" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="163"/>
-      <c r="B113" s="163"/>
-    </row>
-    <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="109" t="s">
+      <c r="B116" s="153"/>
+    </row>
+    <row r="117" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="153"/>
+      <c r="B117" s="153"/>
+    </row>
+    <row r="118" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="109" t="s">
+        <v>158</v>
+      </c>
+      <c r="B118" s="30">
+        <v>562800</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="109" t="s">
+        <v>160</v>
+      </c>
+      <c r="B119" s="30">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="109" t="s">
+        <v>160</v>
+      </c>
+      <c r="B120" s="30">
+        <v>146000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="109" t="s">
         <v>161</v>
       </c>
-      <c r="B114" s="30">
-        <v>562800</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="109" t="s">
-        <v>163</v>
-      </c>
-      <c r="B115" s="30">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="109" t="s">
-        <v>163</v>
-      </c>
-      <c r="B116" s="30">
-        <v>146000</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="109" t="s">
-        <v>164</v>
-      </c>
-      <c r="B117" s="30">
+      <c r="B121" s="30">
         <v>366010</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="109" t="s">
-        <v>165</v>
-      </c>
-      <c r="B118" s="30">
+    <row r="122" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="109" t="s">
+        <v>162</v>
+      </c>
+      <c r="B122" s="30">
         <v>545000</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="109" t="s">
-        <v>162</v>
-      </c>
-      <c r="B119" s="140">
+    <row r="123" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="109" t="s">
+        <v>159</v>
+      </c>
+      <c r="B123" s="140">
         <v>126000</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="42" t="s">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A124" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="B120" s="110">
-        <f>SUM(B114:B119)</f>
+      <c r="B124" s="110">
+        <f>SUM(B118:B123)</f>
         <v>2145810</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L121" s="8"/>
-    </row>
-    <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="162"/>
-      <c r="B122" s="162"/>
-      <c r="C122" s="162"/>
-      <c r="D122" s="162"/>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="162"/>
-      <c r="B123" s="162"/>
-      <c r="C123" s="162"/>
-      <c r="D123" s="162"/>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="162"/>
-      <c r="B124" s="162"/>
-      <c r="C124" s="162"/>
-      <c r="D124" s="162"/>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="162"/>
-      <c r="B125" s="162"/>
-      <c r="C125" s="162"/>
-      <c r="D125" s="162"/>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L125" s="8"/>
+    </row>
+    <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="152"/>
+      <c r="B126" s="152"/>
+      <c r="C126" s="152"/>
+      <c r="D126" s="152"/>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A127" s="152"/>
+      <c r="B127" s="152"/>
+      <c r="C127" s="152"/>
+      <c r="D127" s="152"/>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A128" s="152"/>
+      <c r="B128" s="152"/>
+      <c r="C128" s="152"/>
+      <c r="D128" s="152"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="152"/>
+      <c r="B129" s="152"/>
+      <c r="C129" s="152"/>
+      <c r="D129" s="152"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A122:D125"/>
-    <mergeCell ref="A112:B113"/>
-    <mergeCell ref="A97:D99"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A81:B81"/>
+  <mergeCells count="21">
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A72:B72"/>
     <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A63:B63"/>
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A126:D129"/>
+    <mergeCell ref="A116:B117"/>
+    <mergeCell ref="A101:D103"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A85:B85"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2867,61 +2940,61 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="0.140625" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" customWidth="1"/>
-    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" customWidth="1"/>
+    <col min="5" max="5" width="0.109375" customWidth="1"/>
+    <col min="6" max="6" width="5.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" customWidth="1"/>
+    <col min="12" max="12" width="14.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" customWidth="1"/>
+    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="165" t="s">
+      <c r="B1" s="174" t="s">
         <v>123</v>
       </c>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
-      <c r="G1" s="165"/>
-      <c r="H1" s="165"/>
-      <c r="I1" s="165"/>
-      <c r="J1" s="165"/>
-      <c r="K1" s="165"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="174"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="174"/>
+      <c r="I1" s="174"/>
+      <c r="J1" s="174"/>
+      <c r="K1" s="174"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
-      <c r="B2" s="165"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="165"/>
-      <c r="J2" s="165"/>
-      <c r="K2" s="165"/>
+      <c r="B2" s="174"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -2933,18 +3006,18 @@
       <c r="P2" s="48"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:19" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="166"/>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="166"/>
-      <c r="I3" s="166"/>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="175"/>
+      <c r="K3" s="175"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -2953,79 +3026,79 @@
       <c r="O3" s="49"/>
       <c r="P3" s="53"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="179" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="168" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="181" t="s">
+      <c r="B4" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="169" t="s">
+      <c r="C4" s="172" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="169" t="s">
+      <c r="D4" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="169" t="s">
+      <c r="E4" s="172" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="169" t="s">
+      <c r="F4" s="172" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="169" t="s">
+      <c r="G4" s="172" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="169" t="s">
+      <c r="H4" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="169" t="s">
+      <c r="I4" s="172" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="174" t="s">
+      <c r="J4" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="171" t="s">
+      <c r="K4" s="179" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="171" t="s">
+      <c r="L4" s="179" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="171" t="s">
+      <c r="M4" s="179" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="177" t="s">
+      <c r="N4" s="184" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="167" t="s">
+      <c r="P4" s="176" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="41"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="180"/>
-      <c r="B5" s="182"/>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="169"/>
+      <c r="B5" s="171"/>
       <c r="C5" s="173"/>
       <c r="D5" s="173"/>
-      <c r="E5" s="170"/>
+      <c r="E5" s="178"/>
       <c r="F5" s="173"/>
       <c r="G5" s="173"/>
       <c r="H5" s="173"/>
-      <c r="I5" s="170"/>
-      <c r="J5" s="175"/>
-      <c r="K5" s="172"/>
-      <c r="L5" s="176"/>
-      <c r="M5" s="172"/>
-      <c r="N5" s="178"/>
+      <c r="I5" s="178"/>
+      <c r="J5" s="182"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="183"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="185"/>
       <c r="O5" s="54" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 14/08</v>
-      </c>
-      <c r="P5" s="168"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>VTO 15/09</v>
+      </c>
+      <c r="P5" s="177"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3081,7 +3154,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
@@ -3139,7 +3212,7 @@
       </c>
       <c r="R7" s="41"/>
     </row>
-    <row r="8" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -3193,7 +3266,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
@@ -3250,7 +3323,7 @@
       </c>
       <c r="S9" s="41"/>
     </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -3307,7 +3380,7 @@
       </c>
       <c r="S10" s="41"/>
     </row>
-    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
@@ -3364,17 +3437,17 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="57">
         <v>7</v>
       </c>
-      <c r="C12" s="183" t="s">
+      <c r="C12" s="148" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="183" t="s">
+      <c r="D12" s="148" t="s">
         <v>101</v>
       </c>
       <c r="E12" s="57"/>
@@ -3420,10 +3493,10 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="S12" s="113" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -3479,7 +3552,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3535,7 +3608,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
@@ -3591,7 +3664,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -3648,7 +3721,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
@@ -3704,7 +3777,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -3761,7 +3834,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -3818,7 +3891,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
@@ -3874,7 +3947,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -3932,7 +4005,7 @@
       </c>
       <c r="S21" s="40"/>
     </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -3989,7 +4062,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
@@ -4046,7 +4119,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
@@ -4103,7 +4176,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
@@ -4160,10 +4233,10 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="S25" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -4220,7 +4293,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
@@ -4276,7 +4349,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
@@ -4333,7 +4406,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
@@ -4390,7 +4463,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
@@ -4446,7 +4519,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
@@ -4504,10 +4577,10 @@
       </c>
       <c r="R31" s="113"/>
       <c r="S31" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>27</v>
       </c>
@@ -4564,7 +4637,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
@@ -4610,7 +4683,7 @@
       </c>
       <c r="Q33" s="41"/>
     </row>
-    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="77"/>
       <c r="C34" s="78"/>
       <c r="D34" s="79"/>
@@ -4654,102 +4727,97 @@
         <v>16197192.779999999</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D35" s="45"/>
       <c r="E35" s="45"/>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="162"/>
-      <c r="E37" s="162"/>
-      <c r="F37" s="162"/>
-      <c r="G37" s="162"/>
-      <c r="H37" s="162"/>
-      <c r="I37" s="162"/>
-      <c r="J37" s="162"/>
-      <c r="K37" s="162"/>
-      <c r="L37" s="162"/>
-      <c r="M37" s="162"/>
-      <c r="N37" s="162"/>
-      <c r="O37" s="162"/>
-    </row>
-    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="162"/>
-      <c r="E38" s="162"/>
-      <c r="F38" s="162"/>
-      <c r="G38" s="162"/>
-      <c r="H38" s="162"/>
-      <c r="I38" s="162"/>
-      <c r="J38" s="162"/>
-      <c r="K38" s="162"/>
-      <c r="L38" s="162"/>
-      <c r="M38" s="162"/>
-      <c r="N38" s="162"/>
-      <c r="O38" s="162"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="162"/>
-      <c r="E39" s="162"/>
-      <c r="F39" s="162"/>
-      <c r="G39" s="162"/>
-      <c r="H39" s="162"/>
-      <c r="I39" s="162"/>
-      <c r="J39" s="162"/>
-      <c r="K39" s="162"/>
-      <c r="L39" s="162"/>
-      <c r="M39" s="162"/>
-      <c r="N39" s="162"/>
-      <c r="O39" s="162"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="162"/>
-      <c r="E40" s="162"/>
-      <c r="F40" s="162"/>
-      <c r="G40" s="162"/>
-      <c r="H40" s="162"/>
-      <c r="I40" s="162"/>
-      <c r="J40" s="162"/>
-      <c r="K40" s="162"/>
-      <c r="L40" s="162"/>
-      <c r="M40" s="162"/>
-      <c r="N40" s="162"/>
-      <c r="O40" s="162"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="162"/>
-      <c r="E41" s="162"/>
-      <c r="F41" s="162"/>
-      <c r="G41" s="162"/>
-      <c r="H41" s="162"/>
-      <c r="I41" s="162"/>
-      <c r="J41" s="162"/>
-      <c r="K41" s="162"/>
-      <c r="L41" s="162"/>
-      <c r="M41" s="162"/>
-      <c r="N41" s="162"/>
-      <c r="O41" s="162"/>
-    </row>
-    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="162"/>
-      <c r="E42" s="162"/>
-      <c r="F42" s="162"/>
-      <c r="G42" s="162"/>
-      <c r="H42" s="162"/>
-      <c r="I42" s="162"/>
-      <c r="J42" s="162"/>
-      <c r="K42" s="162"/>
-      <c r="L42" s="162"/>
-      <c r="M42" s="162"/>
-      <c r="N42" s="162"/>
-      <c r="O42" s="162"/>
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D37" s="152"/>
+      <c r="E37" s="152"/>
+      <c r="F37" s="152"/>
+      <c r="G37" s="152"/>
+      <c r="H37" s="152"/>
+      <c r="I37" s="152"/>
+      <c r="J37" s="152"/>
+      <c r="K37" s="152"/>
+      <c r="L37" s="152"/>
+      <c r="M37" s="152"/>
+      <c r="N37" s="152"/>
+      <c r="O37" s="152"/>
+    </row>
+    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D38" s="152"/>
+      <c r="E38" s="152"/>
+      <c r="F38" s="152"/>
+      <c r="G38" s="152"/>
+      <c r="H38" s="152"/>
+      <c r="I38" s="152"/>
+      <c r="J38" s="152"/>
+      <c r="K38" s="152"/>
+      <c r="L38" s="152"/>
+      <c r="M38" s="152"/>
+      <c r="N38" s="152"/>
+      <c r="O38" s="152"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D39" s="152"/>
+      <c r="E39" s="152"/>
+      <c r="F39" s="152"/>
+      <c r="G39" s="152"/>
+      <c r="H39" s="152"/>
+      <c r="I39" s="152"/>
+      <c r="J39" s="152"/>
+      <c r="K39" s="152"/>
+      <c r="L39" s="152"/>
+      <c r="M39" s="152"/>
+      <c r="N39" s="152"/>
+      <c r="O39" s="152"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D40" s="152"/>
+      <c r="E40" s="152"/>
+      <c r="F40" s="152"/>
+      <c r="G40" s="152"/>
+      <c r="H40" s="152"/>
+      <c r="I40" s="152"/>
+      <c r="J40" s="152"/>
+      <c r="K40" s="152"/>
+      <c r="L40" s="152"/>
+      <c r="M40" s="152"/>
+      <c r="N40" s="152"/>
+      <c r="O40" s="152"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D41" s="152"/>
+      <c r="E41" s="152"/>
+      <c r="F41" s="152"/>
+      <c r="G41" s="152"/>
+      <c r="H41" s="152"/>
+      <c r="I41" s="152"/>
+      <c r="J41" s="152"/>
+      <c r="K41" s="152"/>
+      <c r="L41" s="152"/>
+      <c r="M41" s="152"/>
+      <c r="N41" s="152"/>
+      <c r="O41" s="152"/>
+    </row>
+    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D42" s="152"/>
+      <c r="E42" s="152"/>
+      <c r="F42" s="152"/>
+      <c r="G42" s="152"/>
+      <c r="H42" s="152"/>
+      <c r="I42" s="152"/>
+      <c r="J42" s="152"/>
+      <c r="K42" s="152"/>
+      <c r="L42" s="152"/>
+      <c r="M42" s="152"/>
+      <c r="N42" s="152"/>
+      <c r="O42" s="152"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4762,6 +4830,11 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/colombres/Agosto/AGOSTO COLOMBRES 360.xlsx
+++ b/colombres/Agosto/AGOSTO COLOMBRES 360.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\colombres\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3EF8E34-7847-4275-987D-B55007368366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A19E44-A3FE-4C51-AD56-A87D72EA48AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$125</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$121</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="173">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -318,9 +318,6 @@
     <t>PEDRO ARANDA</t>
   </si>
   <si>
-    <t>MAGRO HECTOR</t>
-  </si>
-  <si>
     <t>BASTEGUIETA JUAN</t>
   </si>
   <si>
@@ -394,14 +391,6 @@
   </si>
   <si>
     <t>PACIFICO GARCIA</t>
-  </si>
-  <si>
-    <t>Titular: CONS. DE PROPIETARIOS COLOMBRES 360
-Banco: SUPERVIELLE
-Sucursal: Lomas de Zamora
-CBU: 02700151 10040979780018
-Nº de cuenta: 04097978-001
-Código de Pago Electrónico: abonar con los centavos de la UF</t>
   </si>
   <si>
     <t>ADMINISTRADORA: CAROLINA CANCIANI MP:1148 - CUIT ADMINISTRACION: 27231256879</t>
@@ -426,15 +415,6 @@
     <t>Ortega Daniel O. - CUIT 20-22388558-7 - Servicio - Fumigación</t>
   </si>
   <si>
-    <t>G Group - Ramón Falcón 395, Lomas de Zamora - CUIT 33-71473408-9  - Service grupo electrógeno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinturería Giannoni S.A. - CUIT 30-55691769-4 - Materiales terraza </t>
-  </si>
-  <si>
-    <t>Borel V. Nora - CUIT 27-27273620-6 - Impermeabilización 4 terrazas</t>
-  </si>
-  <si>
     <t>Banco Supervielle  - Gastos bancarios</t>
   </si>
   <si>
@@ -477,106 +457,97 @@
     <t xml:space="preserve">AySA - Cuenta 1266646 </t>
   </si>
   <si>
-    <t>Debito 04/07</t>
-  </si>
-  <si>
-    <t>Debito 14/07</t>
-  </si>
-  <si>
-    <t>Debito 16/07</t>
-  </si>
-  <si>
-    <t>Transf 14/07</t>
-  </si>
-  <si>
-    <t>Transf 29/07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benitez Nicolas - Cambio de automatico tanque de terraza - Administracion anterior </t>
-  </si>
-  <si>
-    <t>Esenciales (Jerez V.)  - Bolsas, cloro, LED, papel, aromatizante - Administracion anterior</t>
-  </si>
-  <si>
-    <t>Transf 08/07</t>
-  </si>
-  <si>
-    <t>Transf 07/07</t>
-  </si>
-  <si>
-    <t>Estudio Juridico - Dra. Berta A Villarreal Carta documento de despido al Sr. Alvarez Sanchez - Administracion anterior</t>
-  </si>
-  <si>
     <t>María Josefina Conti y Nicolás Massaro</t>
   </si>
   <si>
-    <t>Transf no identificada - Colombres Sur - 05/07</t>
-  </si>
-  <si>
-    <t>Deposito en efectivo 07/07</t>
-  </si>
-  <si>
-    <t>Deposito en efectivo 08/07</t>
-  </si>
-  <si>
-    <t>Deposito en efectivo 10/07</t>
-  </si>
-  <si>
-    <t>Deposito en efectivo 11/07</t>
-  </si>
-  <si>
-    <t>Punitorios mal cobrados por administracion saliente</t>
-  </si>
-  <si>
     <t>Mozart Srl</t>
   </si>
   <si>
     <t>SAC neto</t>
   </si>
   <si>
-    <t>Transf 03/07</t>
-  </si>
-  <si>
-    <t>Honorarios administracion anterior</t>
-  </si>
-  <si>
-    <t>Transf 15/07</t>
-  </si>
-  <si>
-    <t>MES QUE VIENE (EN AGOST0 QUEDA PENDIENTE AGREGAR EL TRASPASO DE ADMINISTRACION QUE ES DE $180MIL PESOS</t>
-  </si>
-  <si>
-    <t>Devolucion anticipo SAC mes pasado (Gestionado por administracion saliente)</t>
-  </si>
-  <si>
-    <t>PREVISION ORDINARIA - ARREGLOS DE ASCENSOR QUE SE HICIERON - BOMBAS (QUE SE DEBEN ABONAR EN LOS PRIMEROS DIAS)</t>
-  </si>
-  <si>
-    <t>EL DEPOSITO DEL MES PASADO DE 545.000 ES DE EL</t>
-  </si>
-  <si>
     <t>VTO 15/09</t>
   </si>
   <si>
-    <t xml:space="preserve">Ascensores Premec - Mantenimiento JULIO 2025 </t>
-  </si>
-  <si>
-    <t>Sasa - Servicio de confeccion y liquidacion de datos - JULIO 2025 - Administracion anterior</t>
-  </si>
-  <si>
     <t>Librería - papelera</t>
   </si>
   <si>
-    <t>FAGUAR - Uniforme porteria - CUIT 00-02381237-3</t>
-  </si>
-  <si>
     <t>Transf 20/08</t>
   </si>
   <si>
-    <t>Fotocopias</t>
-  </si>
-  <si>
-    <t>Ascensores Premec - Reparacion y reinstalacion de indicador de posicion según preupuesto aprobado</t>
+    <t>Transf 03/08</t>
+  </si>
+  <si>
+    <t>Debito 06/08</t>
+  </si>
+  <si>
+    <t>Transf 11/08</t>
+  </si>
+  <si>
+    <t>Debito 08/08</t>
+  </si>
+  <si>
+    <t>Traspaso administracion anterior</t>
+  </si>
+  <si>
+    <t>Debito 14/08</t>
+  </si>
+  <si>
+    <t>FAGUAR - Uniforme porteria - CUIT 00-02381237-3 - Gestionado por administracion anterior, pagado por Diego y transferido a su cuenta</t>
+  </si>
+  <si>
+    <t>Frank Matias Wallace - Mantenimiento ascensor Julio</t>
+  </si>
+  <si>
+    <t>Frank Matias Wallace- Reparacion y reinstalacion de indicador de posicion según preupuesto aprobado</t>
+  </si>
+  <si>
+    <t>Efectivo Administracion</t>
+  </si>
+  <si>
+    <t>Deposito ya identificado mes anterior</t>
+  </si>
+  <si>
+    <t>SONIA</t>
+  </si>
+  <si>
+    <t>Colombres Sur</t>
+  </si>
+  <si>
+    <t>Punitorios mal cobrados</t>
+  </si>
+  <si>
+    <t>PREVISION ORDINARIA</t>
+  </si>
+  <si>
+    <t>Transf 31/08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorarios administracion RC </t>
+  </si>
+  <si>
+    <t>Mes de julio</t>
+  </si>
+  <si>
+    <t>Mes de agosto</t>
+  </si>
+  <si>
+    <t>ellos cobran a mes vencido</t>
+  </si>
+  <si>
+    <t>MAGRO LAUTARO - MAGRO DANIELA</t>
+  </si>
+  <si>
+    <t>Titular: CONS. DE PROPIETARIOS COLOMBRES 360 Banco: SUPERVIELLE Sucursal: Lomas de Zamora CBU: 02700151 10040979780018 Nº de cuenta: 04097978-001 Código de Pago Electrónico: abonar con los centavos de la UF</t>
+  </si>
+  <si>
+    <t>Mes de JULIO</t>
+  </si>
+  <si>
+    <t>MES QUE VIENE PENDIENTE UNA FACTURA DE TAUGE Y OTRA FACTURA QUE DEBEMOS EDITAR DE 4600</t>
+  </si>
+  <si>
+    <t>Hay que sacarle $16,000 de punitorios debe quedar sin deuda</t>
   </si>
 </sst>
 </file>
@@ -584,14 +555,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -780,6 +751,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -849,7 +827,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1191,13 +1169,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1205,14 +1192,14 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1220,7 +1207,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1228,44 +1215,44 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="19" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1279,87 +1266,83 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="24" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1373,8 +1356,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1385,26 +1368,48 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="25" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1414,20 +1419,23 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1435,33 +1443,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1516,8 +1497,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1872,113 +1852,113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L129"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L125"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
-        <v>124</v>
-      </c>
-      <c r="B1" s="128"/>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="132" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="124"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="129" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-    </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="129" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="125" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+    </row>
+    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="125" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+    </row>
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="163" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-    </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="158" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="158"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="158"/>
-      <c r="B5" s="158"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="158"/>
-      <c r="B6" s="158"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="130"/>
-    </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="158"/>
-      <c r="B7" s="158"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="157" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="157"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="157"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="167" t="s">
+      <c r="B4" s="163"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="163"/>
+      <c r="B5" s="163"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="163"/>
+      <c r="B6" s="163"/>
+      <c r="C6" s="126"/>
+      <c r="D6" s="126"/>
+    </row>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="163"/>
+      <c r="B7" s="163"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="162" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="162"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="162"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="152" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="167"/>
-      <c r="C14" s="167"/>
-      <c r="D14" s="167"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="167"/>
-      <c r="B15" s="167"/>
-      <c r="C15" s="167"/>
-      <c r="D15" s="167"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="167"/>
-      <c r="B16" s="167"/>
-      <c r="C16" s="167"/>
-      <c r="D16" s="167"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="167"/>
-      <c r="B17" s="167"/>
-      <c r="C17" s="167"/>
-      <c r="D17" s="167"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="152"/>
+      <c r="C14" s="152"/>
+      <c r="D14" s="152"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="152"/>
+      <c r="B15" s="152"/>
+      <c r="C15" s="152"/>
+      <c r="D15" s="152"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="152"/>
+      <c r="B16" s="152"/>
+      <c r="C16" s="152"/>
+      <c r="D16" s="152"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="152"/>
+      <c r="B17" s="152"/>
+      <c r="C17" s="152"/>
+      <c r="D17" s="152"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -1986,7 +1966,7 @@
       <c r="C21" s="9"/>
       <c r="D21" s="13"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="27" t="s">
         <v>80</v>
       </c>
@@ -1994,161 +1974,167 @@
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="122">
-        <v>1144385.8999999999</v>
+        <v>132</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C23" s="119">
+        <v>1193249.3999999999</v>
       </c>
       <c r="D23" s="84"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="122">
-        <v>-466337.9</v>
+      <c r="C24" s="119">
+        <v>-233429.42</v>
       </c>
       <c r="D24" s="84"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="122"/>
+      <c r="C25" s="119">
+        <v>0.75</v>
+      </c>
       <c r="D25" s="84"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
-        <v>165</v>
-      </c>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="122">
-        <v>470408</v>
-      </c>
+      <c r="C26" s="119"/>
       <c r="D26" s="84"/>
       <c r="G26" s="14"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="50" t="s">
         <v>82</v>
       </c>
       <c r="B27" s="50"/>
-      <c r="C27" s="123">
+      <c r="C27" s="120">
         <f>SUM(C23:C26)</f>
-        <v>1148456</v>
+        <v>959820.72999999986</v>
       </c>
       <c r="D27" s="85"/>
-      <c r="G27" s="124"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="135" t="s">
-        <v>138</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="122">
-        <v>1005541.03</v>
+      <c r="F27" s="160" t="s">
+        <v>167</v>
+      </c>
+      <c r="G27" s="161"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="131" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" s="119">
+        <v>886097.5</v>
       </c>
       <c r="D28" s="84"/>
-      <c r="G28" s="124"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F28" s="160"/>
+      <c r="G28" s="161"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="118">
-        <v>-218705.03</v>
+      <c r="C29" s="115">
+        <v>-192726.21</v>
       </c>
       <c r="D29" s="84"/>
       <c r="G29" s="14"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="118"/>
+      <c r="C30" s="115">
+        <v>0.71</v>
+      </c>
       <c r="D30" s="84"/>
       <c r="G30" s="14"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="B31" s="5"/>
-      <c r="C31" s="118">
-        <v>526597</v>
-      </c>
+      <c r="C31" s="115"/>
       <c r="D31" s="84"/>
       <c r="G31" s="14"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="50" t="s">
         <v>82</v>
       </c>
       <c r="B32" s="50"/>
       <c r="C32" s="51">
         <f>SUM(C28:C31)</f>
-        <v>1313433</v>
+        <v>693372</v>
       </c>
       <c r="D32" s="85"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="122">
-        <v>1418273.25</v>
-      </c>
-      <c r="D33" s="134"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C33" s="119">
+        <v>1377300.26</v>
+      </c>
+      <c r="D33" s="130"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B34" s="5"/>
-      <c r="C34" s="122">
-        <v>-308474.25</v>
-      </c>
-      <c r="D34" s="134"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C34" s="119">
+        <v>-299562.81</v>
+      </c>
+      <c r="D34" s="130"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B35" s="5"/>
-      <c r="C35" s="122"/>
-      <c r="D35" s="134"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
-        <v>165</v>
-      </c>
+      <c r="C35" s="119">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D35" s="130"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="5"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="118">
-        <v>690667</v>
-      </c>
-      <c r="D36" s="134"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C36" s="115"/>
+      <c r="D36" s="130"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="133"/>
+      <c r="B37" s="129"/>
       <c r="C37" s="51">
         <f>SUM(C33:C36)</f>
-        <v>1800466</v>
+        <v>1077738</v>
       </c>
       <c r="D37" s="85"/>
     </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
         <v>0</v>
       </c>
@@ -2156,12 +2142,12 @@
       <c r="C38" s="20"/>
       <c r="D38" s="86">
         <f>C27+C32+C37</f>
-        <v>4262355</v>
+        <v>2730930.73</v>
       </c>
       <c r="E38" s="14"/>
       <c r="F38" s="14"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
         <v>38</v>
       </c>
@@ -2170,766 +2156,709 @@
       <c r="D39" s="87"/>
       <c r="F39" s="14"/>
     </row>
-    <row r="40" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="59" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="122"/>
+      <c r="C40" s="119"/>
       <c r="D40" s="88"/>
       <c r="G40" s="14"/>
     </row>
-    <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="137" t="s">
+    <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="133" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="123" t="s">
+        <v>166</v>
+      </c>
+      <c r="C41" s="119">
+        <v>195000</v>
+      </c>
+      <c r="D41" s="88" t="s">
+        <v>163</v>
+      </c>
+      <c r="G41" s="14"/>
+    </row>
+    <row r="42" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="B42" s="123" t="s">
+        <v>165</v>
+      </c>
+      <c r="C42" s="119">
+        <f>C41/2</f>
+        <v>97500</v>
+      </c>
+      <c r="D42" s="88" t="s">
+        <v>163</v>
+      </c>
+      <c r="G42" s="14"/>
+    </row>
+    <row r="43" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="133" t="s">
+        <v>152</v>
+      </c>
+      <c r="B43" s="123"/>
+      <c r="C43" s="119">
+        <v>180000</v>
+      </c>
+      <c r="D43" s="88" t="s">
+        <v>163</v>
+      </c>
+      <c r="G43" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" s="18"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="89">
+        <f>SUM(C40:C43)</f>
+        <v>472500</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" s="26"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="61"/>
+    </row>
+    <row r="46" spans="1:7" s="35" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="150" t="s">
+        <v>129</v>
+      </c>
+      <c r="B46" s="151"/>
+      <c r="C46" s="139">
+        <v>175052</v>
+      </c>
+      <c r="D46" s="116" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="150" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" s="151"/>
+      <c r="C47" s="140">
+        <v>4203</v>
+      </c>
+      <c r="D47" s="111" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="18"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="90">
+        <f>SUM(C46:C47)</f>
+        <v>179255</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="91"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C50" s="31">
+        <v>1494923.37</v>
+      </c>
+      <c r="D50" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="F50" s="134"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" s="110">
+        <v>17314.93</v>
+      </c>
+      <c r="D51" s="116" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C52" s="110">
+        <v>155834.29999999999</v>
+      </c>
+      <c r="D52" s="116" t="str">
+        <f>D51</f>
+        <v>Debito 14/08</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C53" s="110">
+        <v>299113.43</v>
+      </c>
+      <c r="D53" s="117" t="str">
+        <f>D52</f>
+        <v>Debito 14/08</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="90">
+        <f>SUM(C50:C53)</f>
+        <v>1967186.03</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="19"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="91"/>
+    </row>
+    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="127"/>
-      <c r="C41" s="122"/>
-      <c r="D41" s="88"/>
-      <c r="G41" s="14"/>
-    </row>
-    <row r="42" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="137" t="s">
-        <v>167</v>
-      </c>
-      <c r="B42" s="127"/>
-      <c r="C42" s="122">
-        <v>392500</v>
-      </c>
-      <c r="D42" s="141" t="s">
-        <v>168</v>
-      </c>
-      <c r="G42" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="89">
-        <f>SUM(C40:C42)</f>
-        <v>392500</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="B44" s="26"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="61"/>
-    </row>
-    <row r="45" spans="1:7" s="35" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="155" t="s">
-        <v>134</v>
-      </c>
-      <c r="B45" s="156"/>
-      <c r="C45" s="144">
-        <v>175052</v>
-      </c>
-      <c r="D45" s="112" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="155" t="s">
-        <v>135</v>
-      </c>
-      <c r="B46" s="156"/>
-      <c r="C46" s="145">
-        <v>4203</v>
-      </c>
-      <c r="D46" s="112" t="s">
+      <c r="B56" s="5"/>
+      <c r="C56" s="110">
+        <v>519920.12</v>
+      </c>
+      <c r="D56" s="95" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="110">
+        <v>50410.45</v>
+      </c>
+      <c r="D57" s="117" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="110">
+        <v>713548.29</v>
+      </c>
+      <c r="D58" s="95" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="150" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" s="151"/>
+      <c r="C59" s="110">
+        <v>308630</v>
+      </c>
+      <c r="D59" s="128" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B47" s="18"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="90">
-        <f>SUM(C45:C46)</f>
-        <v>179255</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="91"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="187">
-        <v>1494923.37</v>
-      </c>
-      <c r="D49" s="119" t="s">
-        <v>148</v>
-      </c>
-      <c r="F49" s="138"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="186">
-        <v>17314.93</v>
-      </c>
-      <c r="D50" s="119" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="186">
-        <v>155834.29999999999</v>
-      </c>
-      <c r="D51" s="119" t="str">
-        <f>D50</f>
-        <v>Debito 14/07</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="186">
-        <v>299113.43</v>
-      </c>
-      <c r="D52" s="120" t="str">
-        <f>D51</f>
-        <v>Debito 14/07</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B53" s="19"/>
-      <c r="C53" s="34"/>
-      <c r="D53" s="90">
-        <f>SUM(C49:C52)</f>
-        <v>1967186.03</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="19"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="91"/>
-    </row>
-    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>144</v>
-      </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="186">
-        <v>519920.12</v>
-      </c>
-      <c r="D55" s="96" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="186">
-        <v>50410.45</v>
-      </c>
-      <c r="D56" s="120" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="186">
-        <v>713548.29</v>
-      </c>
-      <c r="D57" s="96" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="155" t="s">
-        <v>180</v>
-      </c>
-      <c r="B58" s="156"/>
-      <c r="C58" s="186">
-        <v>308630</v>
-      </c>
-      <c r="D58" s="132" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="161" t="s">
-        <v>174</v>
-      </c>
-      <c r="B59" s="162"/>
-      <c r="C59" s="186">
+    <row r="60" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="158" t="s">
+        <v>155</v>
+      </c>
+      <c r="B60" s="159"/>
+      <c r="C60" s="110">
         <v>158501</v>
       </c>
-      <c r="D59" s="132" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B60" s="126"/>
-      <c r="C60" s="111"/>
-      <c r="D60" s="96"/>
-    </row>
-    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="18" t="s">
+      <c r="D60" s="128" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B61" s="122"/>
+      <c r="C61" s="110"/>
+      <c r="D61" s="95"/>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="18" t="s">
         <v>3</v>
-      </c>
-      <c r="B61" s="18"/>
-      <c r="C61" s="32"/>
-      <c r="D61" s="90">
-        <f>SUM(C55:C60)</f>
-        <v>1751009.8599999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="27" t="s">
-        <v>36</v>
       </c>
       <c r="B62" s="18"/>
       <c r="C62" s="32"/>
-      <c r="D62" s="94"/>
-    </row>
-    <row r="63" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="163" t="s">
-        <v>130</v>
-      </c>
-      <c r="B63" s="164"/>
-      <c r="C63" s="111"/>
-      <c r="D63" s="115"/>
-    </row>
-    <row r="64" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="146" t="s">
-        <v>176</v>
-      </c>
-      <c r="B64" s="147"/>
-      <c r="C64" s="186">
+      <c r="D62" s="90">
+        <f>SUM(C56:C61)</f>
+        <v>1751009.8599999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B63" s="18"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="93"/>
+    </row>
+    <row r="64" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="141" t="s">
+        <v>146</v>
+      </c>
+      <c r="B64" s="142"/>
+      <c r="C64" s="110">
         <v>11000</v>
       </c>
-      <c r="D64" s="115"/>
-    </row>
-    <row r="65" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="146" t="s">
-        <v>179</v>
-      </c>
-      <c r="B65" s="147"/>
-      <c r="C65" s="186">
-        <v>48000</v>
-      </c>
-      <c r="D65" s="115"/>
-    </row>
-    <row r="66" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="163" t="s">
-        <v>131</v>
-      </c>
-      <c r="B66" s="164"/>
-      <c r="C66" s="111"/>
-      <c r="D66" s="114"/>
-    </row>
-    <row r="67" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="165" t="s">
-        <v>132</v>
-      </c>
-      <c r="B67" s="166"/>
-      <c r="C67" s="31"/>
+      <c r="D64" s="143" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="156" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" s="157"/>
+      <c r="C65" s="31">
+        <v>99268</v>
+      </c>
+      <c r="D65" s="128" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" s="27"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="97">
+        <f>SUM(C64:C64)</f>
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B67" s="60"/>
+      <c r="C67" s="20"/>
       <c r="D67" s="93"/>
     </row>
-    <row r="68" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="159" t="s">
-        <v>152</v>
-      </c>
-      <c r="B68" s="160"/>
-      <c r="C68" s="31">
-        <v>250000</v>
-      </c>
-      <c r="D68" s="132" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="159" t="s">
-        <v>177</v>
-      </c>
-      <c r="B69" s="160"/>
-      <c r="C69" s="187">
-        <v>99268</v>
-      </c>
-      <c r="D69" s="132" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="159" t="s">
-        <v>175</v>
-      </c>
-      <c r="B70" s="160"/>
-      <c r="C70" s="31">
-        <v>33429</v>
-      </c>
-      <c r="D70" s="132" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="159" t="s">
-        <v>156</v>
-      </c>
-      <c r="B71" s="160"/>
-      <c r="C71" s="31">
-        <v>70000</v>
-      </c>
-      <c r="D71" s="132" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="159" t="s">
-        <v>153</v>
-      </c>
-      <c r="B72" s="160"/>
-      <c r="C72" s="31">
-        <v>191330</v>
-      </c>
-      <c r="D72" s="132" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="18" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B68" s="5"/>
+      <c r="C68" s="110">
+        <v>56820.35</v>
+      </c>
+      <c r="D68" s="98"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B69" s="5"/>
+      <c r="C69" s="110">
+        <v>115051.34</v>
+      </c>
+      <c r="D69" s="96"/>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B70" s="46"/>
+      <c r="C70" s="99"/>
+      <c r="D70" s="90">
+        <f>SUM(C68:C69)</f>
+        <v>171871.69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="84"/>
+      <c r="D71" s="100"/>
+    </row>
+    <row r="72" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="153" t="s">
+        <v>162</v>
+      </c>
+      <c r="B72" s="154"/>
+      <c r="C72" s="155"/>
+      <c r="D72" s="101"/>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1"/>
+      <c r="C73" s="102"/>
+      <c r="D73" s="103"/>
+      <c r="E73" s="41"/>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B74" s="10"/>
+      <c r="C74" s="104"/>
+      <c r="D74" s="105">
+        <f>(SUM(D29:D72))</f>
+        <v>7283753.3099999996</v>
+      </c>
+      <c r="E74" s="41"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C75" s="102"/>
+      <c r="D75" s="102"/>
+      <c r="F75" s="138"/>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="102"/>
+      <c r="D76" s="102"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B77" s="12"/>
+      <c r="C77" s="106"/>
+      <c r="D77" s="107"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="150"/>
+      <c r="B78" s="151"/>
+      <c r="C78" s="94"/>
+      <c r="D78" s="92"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="150"/>
+      <c r="B79" s="151"/>
+      <c r="C79" s="94"/>
+      <c r="D79" s="92"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="113"/>
+      <c r="B80" s="114"/>
+      <c r="C80" s="94"/>
+      <c r="D80" s="92"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="44"/>
+      <c r="B81" s="43"/>
+      <c r="C81" s="52"/>
+      <c r="D81" s="52">
+        <f>SUM(C78:C80)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B84" s="21"/>
+      <c r="C84" s="22"/>
+      <c r="D84" s="121"/>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="86" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B86" s="10"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="62">
+        <f>D81+D84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="82" t="s">
+        <v>31</v>
+      </c>
+      <c r="B88" s="83">
+        <f>D74</f>
+        <v>7283753.3099999996</v>
+      </c>
+      <c r="C88" s="41"/>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="82" t="s">
+        <v>32</v>
+      </c>
+      <c r="B89" s="83">
+        <f>D74-D72</f>
+        <v>7283753.3099999996</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="B90" s="83">
+        <f>D86-D84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="82" t="s">
+        <v>88</v>
+      </c>
+      <c r="B91" s="83">
+        <f>D86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="149"/>
+      <c r="B94" s="149"/>
+      <c r="C94" s="149"/>
+      <c r="D94" s="149"/>
+    </row>
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="149"/>
+      <c r="B95" s="149"/>
+      <c r="C95" s="149"/>
+      <c r="D95" s="149"/>
+    </row>
+    <row r="96" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="149"/>
+      <c r="B96" s="149"/>
+      <c r="C96" s="149"/>
+      <c r="D96" s="149"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B98" s="37"/>
+    </row>
+    <row r="99" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B99" s="118">
+        <v>-298549.79999999888</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B100" s="38">
+        <f>PRORRATEO!H34</f>
+        <v>13720738.269999998</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B101" s="96">
+        <f>B120</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B102" s="145">
+        <v>-545000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B103" s="145">
+        <v>-562800</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B104" s="145">
+        <v>-400000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B105" s="145">
+        <v>-146000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B106" s="145">
+        <f>-16037-23540</f>
+        <v>-39577</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B107" s="96">
+        <f>-B89</f>
+        <v>-7283753.3099999996</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B108" s="96">
+        <f>-(B90)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B73" s="27"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="98">
-        <f>SUM(C63:C67)</f>
-        <v>59000</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B74" s="60"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="94"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="111">
-        <v>56820.35</v>
-      </c>
-      <c r="D75" s="99"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B76" s="5"/>
-      <c r="C76" s="111">
-        <v>142713.93</v>
-      </c>
-      <c r="D76" s="97"/>
-    </row>
-    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="B77" s="46"/>
-      <c r="C77" s="100"/>
-      <c r="D77" s="90">
-        <f>SUM(C75:C76)</f>
-        <v>199534.28</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="5"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="84"/>
-      <c r="D78" s="101"/>
-    </row>
-    <row r="79" spans="1:5" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="149" t="s">
-        <v>171</v>
-      </c>
-      <c r="B79" s="150"/>
-      <c r="C79" s="151"/>
-      <c r="D79" s="102">
-        <v>2334921.91</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="1"/>
-      <c r="C80" s="103"/>
-      <c r="D80" s="104"/>
-      <c r="E80" s="41"/>
-    </row>
-    <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B81" s="10"/>
-      <c r="C81" s="105"/>
-      <c r="D81" s="106">
-        <f>(SUM(D29:D79))</f>
-        <v>11145762.08</v>
-      </c>
-      <c r="E81" s="41"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C82" s="103"/>
-      <c r="D82" s="103"/>
-      <c r="F82" s="143"/>
-    </row>
-    <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C83" s="103"/>
-      <c r="D83" s="103"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B84" s="12"/>
-      <c r="C84" s="107"/>
-      <c r="D84" s="108"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="155"/>
-      <c r="B85" s="156"/>
-      <c r="C85" s="95"/>
-      <c r="D85" s="92"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="155"/>
-      <c r="B86" s="156"/>
-      <c r="C86" s="95"/>
-      <c r="D86" s="92"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="116"/>
-      <c r="B87" s="117"/>
-      <c r="C87" s="95"/>
-      <c r="D87" s="92"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="44"/>
-      <c r="B88" s="43"/>
-      <c r="C88" s="52"/>
-      <c r="D88" s="52">
-        <f>SUM(C85:C87)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B91" s="21"/>
-      <c r="C91" s="22"/>
-      <c r="D91" s="125"/>
-    </row>
-    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="93" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B93" s="10"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="62">
-        <f>D88+D91</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="95" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="82" t="s">
-        <v>31</v>
-      </c>
-      <c r="B95" s="83">
-        <f>D81</f>
-        <v>11145762.08</v>
-      </c>
-      <c r="C95" s="41"/>
-    </row>
-    <row r="96" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="82" t="s">
-        <v>32</v>
-      </c>
-      <c r="B96" s="83">
-        <f>D81-D79</f>
-        <v>8810840.1699999999</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="B97" s="83">
-        <f>D93-D91</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="82" t="s">
-        <v>88</v>
-      </c>
-      <c r="B98" s="83">
-        <f>D93</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="154"/>
-      <c r="B101" s="154"/>
-      <c r="C101" s="154"/>
-      <c r="D101" s="154"/>
-    </row>
-    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="154"/>
-      <c r="B102" s="154"/>
-      <c r="C102" s="154"/>
-      <c r="D102" s="154"/>
-    </row>
-    <row r="103" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="154"/>
-      <c r="B103" s="154"/>
-      <c r="C103" s="154"/>
-      <c r="D103" s="154"/>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B105" s="37"/>
-    </row>
-    <row r="106" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B106" s="121">
-        <v>-847927.83</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B107" s="38">
-        <f>PRORRATEO!H34</f>
-        <v>9758198.1199999992</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B108" s="97">
-        <f>B124</f>
-        <v>2145810</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="B109" s="97">
-        <v>-1650000</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="B110" s="97">
-        <v>-39552</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="B111" s="97">
-        <f>-B96</f>
-        <v>-8810840.1699999999</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B112" s="97">
-        <f>-(B97)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A113" s="23" t="s">
+      <c r="B109" s="118">
+        <f>SUM(B99:B108)</f>
+        <v>4445058.1599999992</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="39"/>
+      <c r="C110" s="41"/>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="148" t="s">
+        <v>78</v>
+      </c>
+      <c r="B112" s="148"/>
+    </row>
+    <row r="113" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="148"/>
+      <c r="B113" s="148"/>
+    </row>
+    <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="108"/>
+      <c r="B114" s="30"/>
+    </row>
+    <row r="115" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="108"/>
+      <c r="B115" s="30"/>
+    </row>
+    <row r="116" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="108"/>
+      <c r="B116" s="30"/>
+    </row>
+    <row r="117" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="108"/>
+      <c r="B117" s="30"/>
+    </row>
+    <row r="118" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="108"/>
+      <c r="B118" s="30"/>
+    </row>
+    <row r="119" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="108"/>
+      <c r="B119" s="136"/>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="B113" s="121">
-        <f>SUM(B106:B112)</f>
-        <v>555688.11999999918</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B114" s="39"/>
-      <c r="C114" s="41"/>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A116" s="153" t="s">
-        <v>78</v>
-      </c>
-      <c r="B116" s="153"/>
-    </row>
-    <row r="117" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="153"/>
-      <c r="B117" s="153"/>
-    </row>
-    <row r="118" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="109" t="s">
-        <v>158</v>
-      </c>
-      <c r="B118" s="30">
-        <v>562800</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="109" t="s">
-        <v>160</v>
-      </c>
-      <c r="B119" s="30">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="109" t="s">
-        <v>160</v>
-      </c>
-      <c r="B120" s="30">
-        <v>146000</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="109" t="s">
-        <v>161</v>
-      </c>
-      <c r="B121" s="30">
-        <v>366010</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="109" t="s">
-        <v>162</v>
-      </c>
-      <c r="B122" s="30">
-        <v>545000</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="109" t="s">
-        <v>159</v>
-      </c>
-      <c r="B123" s="140">
-        <v>126000</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A124" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="B124" s="110">
-        <f>SUM(B118:B123)</f>
-        <v>2145810</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L125" s="8"/>
-    </row>
-    <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="152"/>
-      <c r="B126" s="152"/>
-      <c r="C126" s="152"/>
-      <c r="D126" s="152"/>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A127" s="152"/>
-      <c r="B127" s="152"/>
-      <c r="C127" s="152"/>
-      <c r="D127" s="152"/>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A128" s="152"/>
-      <c r="B128" s="152"/>
-      <c r="C128" s="152"/>
-      <c r="D128" s="152"/>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="152"/>
-      <c r="B129" s="152"/>
-      <c r="C129" s="152"/>
-      <c r="D129" s="152"/>
+      <c r="B120" s="109">
+        <f>SUM(B114:B119)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L121" s="8"/>
+    </row>
+    <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="147"/>
+      <c r="B122" s="147"/>
+      <c r="C122" s="147"/>
+      <c r="D122" s="147"/>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" s="147"/>
+      <c r="B123" s="147"/>
+      <c r="C123" s="147"/>
+      <c r="D123" s="147"/>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" s="147"/>
+      <c r="B124" s="147"/>
+      <c r="C124" s="147"/>
+      <c r="D124" s="147"/>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" s="147"/>
+      <c r="B125" s="147"/>
+      <c r="C125" s="147"/>
+      <c r="D125" s="147"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="15">
+    <mergeCell ref="F27:G28"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A59:B59"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A126:D129"/>
-    <mergeCell ref="A116:B117"/>
-    <mergeCell ref="A101:D103"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A122:D125"/>
+    <mergeCell ref="A112:B113"/>
+    <mergeCell ref="A94:D96"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A78:B78"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2940,84 +2869,84 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="0.109375" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="0.140625" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="174" t="s">
-        <v>123</v>
-      </c>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="174"/>
+      <c r="B1" s="170" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="174"/>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174"/>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
+      <c r="B2" s="170"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="170"/>
+      <c r="K2" s="170"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="142">
-        <v>12000000</v>
+      <c r="O2" s="137">
+        <v>7000000</v>
       </c>
       <c r="P2" s="48"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:19" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="175"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -3026,79 +2955,79 @@
       <c r="O3" s="49"/>
       <c r="P3" s="53"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="168" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="164" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="170" t="s">
+      <c r="B4" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="172" t="s">
+      <c r="C4" s="168" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="172" t="s">
+      <c r="D4" s="168" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="172" t="s">
+      <c r="E4" s="168" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="172" t="s">
+      <c r="F4" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="172" t="s">
+      <c r="G4" s="168" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="172" t="s">
+      <c r="H4" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="172" t="s">
+      <c r="I4" s="168" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="181" t="s">
+      <c r="J4" s="177" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="179" t="s">
+      <c r="K4" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="179" t="s">
+      <c r="L4" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="179" t="s">
+      <c r="M4" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="184" t="s">
+      <c r="N4" s="180" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="176" t="s">
+      <c r="P4" s="172" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="41"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="169"/>
-      <c r="B5" s="171"/>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="178"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
-      <c r="I5" s="178"/>
-      <c r="J5" s="182"/>
-      <c r="K5" s="180"/>
-      <c r="L5" s="183"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="185"/>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="165"/>
+      <c r="B5" s="167"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="169"/>
+      <c r="H5" s="169"/>
+      <c r="I5" s="174"/>
+      <c r="J5" s="178"/>
+      <c r="K5" s="176"/>
+      <c r="L5" s="179"/>
+      <c r="M5" s="176"/>
+      <c r="N5" s="181"/>
       <c r="O5" s="54" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/09</v>
       </c>
-      <c r="P5" s="177"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P5" s="173"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3116,11 +3045,10 @@
         <v>4.57</v>
       </c>
       <c r="G6" s="64">
-        <v>548400.01</v>
+        <v>553400.01</v>
       </c>
       <c r="H6" s="65">
-        <f>158442+389958</f>
-        <v>548400</v>
+        <v>553400</v>
       </c>
       <c r="I6" s="66"/>
       <c r="J6" s="67">
@@ -3137,24 +3065,24 @@
       </c>
       <c r="M6" s="68">
         <f>O$2*F6%</f>
-        <v>548400</v>
+        <v>319900.00000000006</v>
       </c>
       <c r="N6" s="69">
         <v>5000</v>
       </c>
       <c r="O6" s="70">
         <f t="shared" ref="O6:O33" si="0">ROUND(SUM(J6:N6),0) + Q6</f>
-        <v>553400.01</v>
+        <v>324900.01</v>
       </c>
       <c r="P6" s="71">
         <f t="shared" ref="P6:P33" si="1">ROUND(O6*3%,0) + O6</f>
-        <v>570002.01</v>
+        <v>334647.01</v>
       </c>
       <c r="Q6" s="41">
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
@@ -3172,16 +3100,15 @@
         <v>3.07</v>
       </c>
       <c r="G7" s="64">
-        <v>368400.02</v>
+        <v>192203</v>
       </c>
       <c r="H7" s="65">
-        <f>300000+255195</f>
-        <v>555195</v>
+        <v>192203</v>
       </c>
       <c r="I7" s="66"/>
       <c r="J7" s="67">
         <f t="shared" ref="J7:J31" si="2">G7-H7</f>
-        <v>-186794.97999999998</v>
+        <v>0</v>
       </c>
       <c r="K7" s="67">
         <f t="shared" ref="K7:K32" si="3">IF(J7&gt;0,J7*2.95%,0)</f>
@@ -3193,18 +3120,18 @@
       </c>
       <c r="M7" s="68">
         <f t="shared" ref="M7:M33" si="5">O$2*F7%</f>
-        <v>368400</v>
+        <v>214900</v>
       </c>
       <c r="N7" s="69">
         <v>5000</v>
       </c>
       <c r="O7" s="70">
         <f t="shared" si="0"/>
-        <v>186605.02</v>
+        <v>219900.02</v>
       </c>
       <c r="P7" s="71">
         <f t="shared" si="1"/>
-        <v>192203.02</v>
+        <v>226497.02</v>
       </c>
       <c r="Q7" s="41">
         <f>Q6+0.01</f>
@@ -3212,7 +3139,7 @@
       </c>
       <c r="R7" s="41"/>
     </row>
-    <row r="8" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -3222,27 +3149,27 @@
       <c r="C8" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="57" t="s">
-        <v>97</v>
+      <c r="D8" s="146" t="s">
+        <v>168</v>
       </c>
       <c r="E8" s="58"/>
       <c r="F8" s="63">
         <v>4.55</v>
       </c>
       <c r="G8" s="64">
-        <v>1719204.03</v>
+        <v>2315921.0299999998</v>
       </c>
       <c r="H8" s="65">
-        <v>0</v>
+        <v>546000</v>
       </c>
       <c r="I8" s="66"/>
       <c r="J8" s="67">
         <f t="shared" si="2"/>
-        <v>1719204.03</v>
+        <v>1769921.0299999998</v>
       </c>
       <c r="K8" s="67">
         <f t="shared" si="3"/>
-        <v>50716.518885000005</v>
+        <v>52212.670384999998</v>
       </c>
       <c r="L8" s="68">
         <f t="shared" si="4"/>
@@ -3250,23 +3177,23 @@
       </c>
       <c r="M8" s="68">
         <f t="shared" si="5"/>
-        <v>546000</v>
+        <v>318500</v>
       </c>
       <c r="N8" s="69"/>
       <c r="O8" s="70">
         <f t="shared" si="0"/>
-        <v>2315921.0299999998</v>
+        <v>2140634.0299999998</v>
       </c>
       <c r="P8" s="71">
         <f t="shared" si="1"/>
-        <v>2385399.0299999998</v>
+        <v>2204853.0299999998</v>
       </c>
       <c r="Q8" s="41">
         <f t="shared" ref="Q8:Q32" si="6">Q7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
@@ -3277,22 +3204,23 @@
         <v>54</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E9" s="58"/>
       <c r="F9" s="63">
         <v>3.05</v>
       </c>
       <c r="G9" s="64">
-        <v>352902.04</v>
+        <v>318902.03999999998</v>
       </c>
       <c r="H9" s="65">
-        <v>400000.04</v>
+        <f>300000+100000</f>
+        <v>400000</v>
       </c>
       <c r="I9" s="66"/>
       <c r="J9" s="67">
         <f t="shared" si="2"/>
-        <v>-47098</v>
+        <v>-81097.960000000021</v>
       </c>
       <c r="K9" s="67">
         <f t="shared" si="3"/>
@@ -3304,26 +3232,29 @@
       </c>
       <c r="M9" s="68">
         <f t="shared" si="5"/>
-        <v>366000</v>
+        <v>213500</v>
       </c>
       <c r="N9" s="69">
         <v>0</v>
       </c>
       <c r="O9" s="70">
         <f t="shared" si="0"/>
-        <v>318902.03999999998</v>
+        <v>132402.04</v>
       </c>
       <c r="P9" s="71">
         <f t="shared" si="1"/>
-        <v>328469.03999999998</v>
+        <v>136374.04</v>
       </c>
       <c r="Q9" s="41">
         <f t="shared" si="6"/>
         <v>0.04</v>
       </c>
+      <c r="R9" t="s">
+        <v>159</v>
+      </c>
       <c r="S9" s="41"/>
     </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -3334,22 +3265,22 @@
         <v>55</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E10" s="58"/>
       <c r="F10" s="63">
         <v>4.55</v>
       </c>
       <c r="G10" s="64">
-        <v>545848.05000000005</v>
+        <v>541848.05000000005</v>
       </c>
       <c r="H10" s="65">
-        <v>550000</v>
+        <v>542000</v>
       </c>
       <c r="I10" s="66"/>
       <c r="J10" s="67">
         <f t="shared" si="2"/>
-        <v>-4151.9499999999534</v>
+        <v>-151.94999999995343</v>
       </c>
       <c r="K10" s="67">
         <f t="shared" si="3"/>
@@ -3361,18 +3292,18 @@
       </c>
       <c r="M10" s="68">
         <f t="shared" si="5"/>
-        <v>546000</v>
+        <v>318500</v>
       </c>
       <c r="N10" s="69">
         <v>0</v>
       </c>
       <c r="O10" s="70">
         <f t="shared" si="0"/>
-        <v>541848.05000000005</v>
+        <v>318348.05</v>
       </c>
       <c r="P10" s="71">
         <f t="shared" si="1"/>
-        <v>558103.05000000005</v>
+        <v>327898.05</v>
       </c>
       <c r="Q10" s="41">
         <f t="shared" si="6"/>
@@ -3380,7 +3311,7 @@
       </c>
       <c r="S10" s="41"/>
     </row>
-    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
@@ -3391,23 +3322,22 @@
         <v>56</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E11" s="57"/>
       <c r="F11" s="63">
         <v>3.05</v>
       </c>
       <c r="G11" s="64">
-        <v>366000.06</v>
+        <v>371000.06</v>
       </c>
       <c r="H11" s="65">
-        <f>G11</f>
-        <v>366000.06</v>
+        <v>382130.06</v>
       </c>
       <c r="I11" s="66"/>
       <c r="J11" s="67">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-11130</v>
       </c>
       <c r="K11" s="67">
         <f t="shared" si="3"/>
@@ -3419,55 +3349,56 @@
       </c>
       <c r="M11" s="68">
         <f t="shared" si="5"/>
-        <v>366000</v>
+        <v>213500</v>
       </c>
       <c r="N11" s="69">
         <v>5000</v>
       </c>
       <c r="O11" s="70">
         <f t="shared" si="0"/>
-        <v>371000.06</v>
+        <v>207370.06</v>
       </c>
       <c r="P11" s="71">
         <f t="shared" si="1"/>
-        <v>382130.06</v>
+        <v>213591.06</v>
       </c>
       <c r="Q11" s="41">
         <f t="shared" si="6"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="57">
         <v>7</v>
       </c>
-      <c r="C12" s="148" t="s">
+      <c r="C12" s="144" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="148" t="s">
-        <v>101</v>
+      <c r="D12" s="144" t="s">
+        <v>100</v>
       </c>
       <c r="E12" s="57"/>
       <c r="F12" s="63">
         <v>4.55</v>
       </c>
       <c r="G12" s="64">
-        <v>543639.06999999995</v>
+        <v>1105676.07</v>
       </c>
       <c r="H12" s="65">
-        <v>0</v>
+        <f>400000+144000+545000</f>
+        <v>1089000</v>
       </c>
       <c r="I12" s="66"/>
       <c r="J12" s="67">
         <f t="shared" si="2"/>
-        <v>543639.06999999995</v>
+        <v>16676.070000000065</v>
       </c>
       <c r="K12" s="67">
         <f t="shared" si="3"/>
-        <v>16037.352564999999</v>
+        <v>491.94406500000196</v>
       </c>
       <c r="L12" s="68">
         <f t="shared" si="4"/>
@@ -3475,28 +3406,26 @@
       </c>
       <c r="M12" s="68">
         <f t="shared" si="5"/>
-        <v>546000</v>
+        <v>318500</v>
       </c>
       <c r="N12" s="69">
         <v>0</v>
       </c>
       <c r="O12" s="70">
         <f t="shared" si="0"/>
-        <v>1105676.07</v>
+        <v>335668.07</v>
       </c>
       <c r="P12" s="71">
         <f t="shared" si="1"/>
-        <v>1138846.07</v>
+        <v>345738.07</v>
       </c>
       <c r="Q12" s="41">
         <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="S12" s="113" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S12" s="134"/>
+    </row>
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -3507,26 +3436,26 @@
         <v>58</v>
       </c>
       <c r="D13" s="57" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E13" s="58"/>
       <c r="F13" s="63">
         <v>3.05</v>
       </c>
       <c r="G13" s="64">
-        <v>366000.08</v>
+        <v>742797.08</v>
       </c>
       <c r="H13" s="65">
-        <v>0</v>
+        <v>366000</v>
       </c>
       <c r="I13" s="66"/>
       <c r="J13" s="67">
         <f t="shared" si="2"/>
-        <v>366000.08</v>
+        <v>376797.07999999996</v>
       </c>
       <c r="K13" s="67">
         <f t="shared" si="3"/>
-        <v>10797.00236</v>
+        <v>11115.513859999999</v>
       </c>
       <c r="L13" s="68">
         <f t="shared" si="4"/>
@@ -3534,25 +3463,25 @@
       </c>
       <c r="M13" s="68">
         <f t="shared" si="5"/>
-        <v>366000</v>
+        <v>213500</v>
       </c>
       <c r="N13" s="69">
         <v>0</v>
       </c>
       <c r="O13" s="70">
         <f t="shared" si="0"/>
-        <v>742797.08</v>
+        <v>601413.07999999996</v>
       </c>
       <c r="P13" s="71">
         <f t="shared" si="1"/>
-        <v>765081.08</v>
+        <v>619455.07999999996</v>
       </c>
       <c r="Q13" s="41">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3563,26 +3492,27 @@
         <v>59</v>
       </c>
       <c r="D14" s="57" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E14" s="58"/>
       <c r="F14" s="63">
         <v>4.5599999999999996</v>
       </c>
       <c r="G14" s="64">
-        <v>545707.09</v>
-      </c>
-      <c r="H14" s="65">
-        <v>0</v>
+        <v>1109005.0900000001</v>
+      </c>
+      <c r="H14" s="66">
+        <f>400000+146000+547000</f>
+        <v>1093000</v>
       </c>
       <c r="I14" s="66"/>
-      <c r="J14" s="67">
+      <c r="J14" s="182">
         <f t="shared" si="2"/>
-        <v>545707.09</v>
+        <v>16005.090000000084</v>
       </c>
       <c r="K14" s="67">
         <f t="shared" si="3"/>
-        <v>16098.359155</v>
+        <v>472.15015500000248</v>
       </c>
       <c r="L14" s="68">
         <f t="shared" si="4"/>
@@ -3590,25 +3520,28 @@
       </c>
       <c r="M14" s="68">
         <f t="shared" si="5"/>
-        <v>547199.99999999988</v>
+        <v>319199.99999999994</v>
       </c>
       <c r="N14" s="69">
         <v>0</v>
       </c>
       <c r="O14" s="70">
         <f t="shared" si="0"/>
-        <v>1109005.0900000001</v>
+        <v>335677.09</v>
       </c>
       <c r="P14" s="71">
         <f t="shared" si="1"/>
-        <v>1142275.0900000001</v>
+        <v>345747.09</v>
       </c>
       <c r="Q14" s="41">
         <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
@@ -3619,7 +3552,7 @@
         <v>60</v>
       </c>
       <c r="D15" s="57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E15" s="58"/>
       <c r="F15" s="63">
@@ -3629,12 +3562,12 @@
         <v>365999.1</v>
       </c>
       <c r="H15" s="65">
-        <v>366000</v>
+        <v>365999.1</v>
       </c>
       <c r="I15" s="66"/>
       <c r="J15" s="67">
         <f t="shared" si="2"/>
-        <v>-0.90000000002328306</v>
+        <v>0</v>
       </c>
       <c r="K15" s="67">
         <f t="shared" si="3"/>
@@ -3646,25 +3579,25 @@
       </c>
       <c r="M15" s="68">
         <f t="shared" si="5"/>
-        <v>366000</v>
+        <v>213500</v>
       </c>
       <c r="N15" s="69">
         <v>0</v>
       </c>
       <c r="O15" s="70">
         <f t="shared" si="0"/>
-        <v>365999.1</v>
+        <v>213500.1</v>
       </c>
       <c r="P15" s="71">
         <f t="shared" si="1"/>
-        <v>376979.1</v>
+        <v>219905.1</v>
       </c>
       <c r="Q15" s="41">
         <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -3675,7 +3608,7 @@
         <v>61</v>
       </c>
       <c r="D16" s="57" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E16" s="58"/>
       <c r="F16" s="63">
@@ -3703,25 +3636,25 @@
       </c>
       <c r="M16" s="68">
         <f t="shared" si="5"/>
-        <v>546000</v>
+        <v>318500</v>
       </c>
       <c r="N16" s="69">
         <v>0</v>
       </c>
       <c r="O16" s="70">
         <f t="shared" si="0"/>
-        <v>546000.11</v>
+        <v>318500.11</v>
       </c>
       <c r="P16" s="71">
         <f t="shared" si="1"/>
-        <v>562380.11</v>
+        <v>328055.11</v>
       </c>
       <c r="Q16" s="41">
         <f t="shared" si="6"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
@@ -3732,26 +3665,27 @@
         <v>62</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E17" s="58"/>
       <c r="F17" s="63">
         <v>3.05</v>
       </c>
       <c r="G17" s="64">
-        <v>125926.12</v>
+        <v>495641.12</v>
       </c>
       <c r="H17" s="65">
-        <v>0</v>
+        <f>200000+300000</f>
+        <v>500000</v>
       </c>
       <c r="I17" s="66"/>
       <c r="J17" s="67">
         <f t="shared" si="2"/>
-        <v>125926.12</v>
+        <v>-4358.8800000000047</v>
       </c>
       <c r="K17" s="67">
         <f t="shared" si="3"/>
-        <v>3714.8205400000002</v>
+        <v>0</v>
       </c>
       <c r="L17" s="68">
         <f t="shared" si="4"/>
@@ -3759,25 +3693,25 @@
       </c>
       <c r="M17" s="68">
         <f t="shared" si="5"/>
-        <v>366000</v>
+        <v>213500</v>
       </c>
       <c r="N17" s="69">
         <v>0</v>
       </c>
       <c r="O17" s="70">
         <f t="shared" si="0"/>
-        <v>495641.12</v>
+        <v>209141.12</v>
       </c>
       <c r="P17" s="71">
         <f t="shared" si="1"/>
-        <v>510510.12</v>
+        <v>215415.12</v>
       </c>
       <c r="Q17" s="41">
         <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -3788,7 +3722,7 @@
         <v>63</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E18" s="58"/>
       <c r="F18" s="63">
@@ -3816,25 +3750,25 @@
       </c>
       <c r="M18" s="68">
         <f t="shared" si="5"/>
-        <v>546000</v>
+        <v>318500</v>
       </c>
       <c r="N18" s="69">
         <v>0</v>
       </c>
       <c r="O18" s="70">
         <f t="shared" si="0"/>
-        <v>546000.13</v>
+        <v>318500.13</v>
       </c>
       <c r="P18" s="71">
         <f t="shared" si="1"/>
-        <v>562380.13</v>
+        <v>328055.13</v>
       </c>
       <c r="Q18" s="41">
         <f t="shared" si="6"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -3845,7 +3779,7 @@
         <v>64</v>
       </c>
       <c r="D19" s="57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E19" s="58"/>
       <c r="F19" s="63">
@@ -3873,25 +3807,25 @@
       </c>
       <c r="M19" s="68">
         <f t="shared" si="5"/>
-        <v>381600</v>
+        <v>222600</v>
       </c>
       <c r="N19" s="69">
         <v>0</v>
       </c>
       <c r="O19" s="70">
         <f t="shared" si="0"/>
-        <v>381600.14</v>
+        <v>222600.14</v>
       </c>
       <c r="P19" s="71">
         <f t="shared" si="1"/>
-        <v>393048.14</v>
+        <v>229278.14</v>
       </c>
       <c r="Q19" s="41">
         <f t="shared" si="6"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
@@ -3902,22 +3836,23 @@
         <v>65</v>
       </c>
       <c r="D20" s="57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E20" s="58"/>
       <c r="F20" s="63">
         <v>4.55</v>
       </c>
       <c r="G20" s="64">
-        <v>546000.15</v>
+        <v>518700.15</v>
       </c>
       <c r="H20" s="65">
-        <v>573300.15</v>
+        <f>G20</f>
+        <v>518700.15</v>
       </c>
       <c r="I20" s="66"/>
       <c r="J20" s="67">
         <f t="shared" si="2"/>
-        <v>-27300</v>
+        <v>0</v>
       </c>
       <c r="K20" s="67">
         <f t="shared" si="3"/>
@@ -3929,25 +3864,25 @@
       </c>
       <c r="M20" s="68">
         <f t="shared" si="5"/>
-        <v>546000</v>
+        <v>318500</v>
       </c>
       <c r="N20" s="69">
         <v>0</v>
       </c>
       <c r="O20" s="70">
         <f t="shared" si="0"/>
-        <v>518700.15</v>
+        <v>318500.15000000002</v>
       </c>
       <c r="P20" s="71">
         <f t="shared" si="1"/>
-        <v>534261.15</v>
+        <v>328055.15000000002</v>
       </c>
       <c r="Q20" s="41">
         <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -3958,7 +3893,7 @@
         <v>66</v>
       </c>
       <c r="D21" s="57" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E21" s="57"/>
       <c r="F21" s="63">
@@ -3986,18 +3921,18 @@
       </c>
       <c r="M21" s="68">
         <f t="shared" si="5"/>
-        <v>380400</v>
+        <v>221900</v>
       </c>
       <c r="N21" s="69">
         <v>0</v>
       </c>
       <c r="O21" s="70">
         <f t="shared" si="0"/>
-        <v>380400.16</v>
+        <v>221900.16</v>
       </c>
       <c r="P21" s="71">
         <f t="shared" si="1"/>
-        <v>391812.16</v>
+        <v>228557.16</v>
       </c>
       <c r="Q21" s="41">
         <f t="shared" si="6"/>
@@ -4005,7 +3940,7 @@
       </c>
       <c r="S21" s="40"/>
     </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -4016,18 +3951,18 @@
         <v>67</v>
       </c>
       <c r="D22" s="57" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E22" s="58"/>
       <c r="F22" s="63">
         <v>4.55</v>
       </c>
       <c r="G22" s="65">
-        <v>546000.17000000004</v>
+        <v>562380.17000000004</v>
       </c>
       <c r="H22" s="65">
         <f>G22</f>
-        <v>546000.17000000004</v>
+        <v>562380.17000000004</v>
       </c>
       <c r="I22" s="66"/>
       <c r="J22" s="67">
@@ -4044,25 +3979,25 @@
       </c>
       <c r="M22" s="68">
         <f t="shared" si="5"/>
-        <v>546000</v>
+        <v>318500</v>
       </c>
       <c r="N22" s="69">
         <v>0</v>
       </c>
       <c r="O22" s="70">
         <f t="shared" si="0"/>
-        <v>546000.17000000004</v>
+        <v>318500.17</v>
       </c>
       <c r="P22" s="71">
         <f t="shared" si="1"/>
-        <v>562380.17000000004</v>
+        <v>328055.17</v>
       </c>
       <c r="Q22" s="41">
         <f t="shared" si="6"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
@@ -4073,7 +4008,7 @@
         <v>68</v>
       </c>
       <c r="D23" s="57" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E23" s="57"/>
       <c r="F23" s="63">
@@ -4083,13 +4018,12 @@
         <v>380400.18</v>
       </c>
       <c r="H23" s="65">
-        <f>G23</f>
-        <v>380400.18</v>
+        <v>391312.18</v>
       </c>
       <c r="I23" s="66"/>
       <c r="J23" s="67">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-10912</v>
       </c>
       <c r="K23" s="67">
         <f t="shared" si="3"/>
@@ -4101,25 +4035,25 @@
       </c>
       <c r="M23" s="68">
         <f t="shared" si="5"/>
-        <v>380400</v>
+        <v>221900</v>
       </c>
       <c r="N23" s="69">
         <v>0</v>
       </c>
       <c r="O23" s="70">
         <f t="shared" si="0"/>
-        <v>380400.18</v>
+        <v>210988.18</v>
       </c>
       <c r="P23" s="71">
         <f t="shared" si="1"/>
-        <v>391812.18</v>
+        <v>217318.18</v>
       </c>
       <c r="Q23" s="41">
         <f t="shared" si="6"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
@@ -4130,23 +4064,23 @@
         <v>69</v>
       </c>
       <c r="D24" s="57" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E24" s="58"/>
       <c r="F24" s="63">
         <v>4.55</v>
       </c>
       <c r="G24" s="64">
-        <v>1438864.19</v>
-      </c>
-      <c r="H24" s="139">
-        <f>388251.19+546000.19+465061.19+39552</f>
-        <v>1438864.5699999998</v>
+        <v>546000.18999999994</v>
+      </c>
+      <c r="H24" s="135">
+        <f>G24</f>
+        <v>546000.18999999994</v>
       </c>
       <c r="I24" s="66"/>
       <c r="J24" s="67">
         <f t="shared" si="2"/>
-        <v>-0.37999999988824129</v>
+        <v>0</v>
       </c>
       <c r="K24" s="67">
         <f t="shared" si="3"/>
@@ -4158,25 +4092,25 @@
       </c>
       <c r="M24" s="68">
         <f t="shared" si="5"/>
-        <v>546000</v>
+        <v>318500</v>
       </c>
       <c r="N24" s="69">
         <v>0</v>
       </c>
       <c r="O24" s="70">
         <f t="shared" si="0"/>
-        <v>546000.18999999994</v>
+        <v>318500.19</v>
       </c>
       <c r="P24" s="71">
         <f t="shared" si="1"/>
-        <v>562380.18999999994</v>
+        <v>328055.19</v>
       </c>
       <c r="Q24" s="41">
         <f t="shared" si="6"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
@@ -4187,7 +4121,7 @@
         <v>70</v>
       </c>
       <c r="D25" s="57" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E25" s="57"/>
       <c r="F25" s="63">
@@ -4215,28 +4149,28 @@
       </c>
       <c r="M25" s="68">
         <f t="shared" si="5"/>
-        <v>380400</v>
+        <v>221900</v>
       </c>
       <c r="N25" s="69">
         <v>0</v>
       </c>
       <c r="O25" s="70">
         <f t="shared" si="0"/>
-        <v>380400.2</v>
+        <v>221900.2</v>
       </c>
       <c r="P25" s="71">
         <f t="shared" si="1"/>
-        <v>391812.2</v>
+        <v>228557.2</v>
       </c>
       <c r="Q25" s="41">
         <f t="shared" si="6"/>
         <v>0.20000000000000004</v>
       </c>
       <c r="S25" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -4247,7 +4181,7 @@
         <v>71</v>
       </c>
       <c r="D26" s="57" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E26" s="58"/>
       <c r="F26" s="63">
@@ -4257,13 +4191,12 @@
         <v>546000.21</v>
       </c>
       <c r="H26" s="65">
-        <f>G26</f>
-        <v>546000.21</v>
+        <v>550000.21</v>
       </c>
       <c r="I26" s="66"/>
       <c r="J26" s="67">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="K26" s="67">
         <f t="shared" si="3"/>
@@ -4275,25 +4208,25 @@
       </c>
       <c r="M26" s="68">
         <f t="shared" si="5"/>
-        <v>546000</v>
+        <v>318500</v>
       </c>
       <c r="N26" s="69">
         <v>0</v>
       </c>
       <c r="O26" s="70">
         <f t="shared" si="0"/>
-        <v>546000.21</v>
+        <v>314500.21000000002</v>
       </c>
       <c r="P26" s="71">
         <f t="shared" si="1"/>
-        <v>562380.21</v>
+        <v>323935.21000000002</v>
       </c>
       <c r="Q26" s="41">
         <f t="shared" si="6"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
@@ -4304,22 +4237,23 @@
         <v>72</v>
       </c>
       <c r="D27" s="57" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E27" s="58"/>
       <c r="F27" s="63">
         <v>3.17</v>
       </c>
       <c r="G27" s="64">
-        <v>-1470.22</v>
+        <v>378930.22</v>
       </c>
       <c r="H27" s="65">
-        <v>0</v>
+        <f>381870.22</f>
+        <v>381870.22</v>
       </c>
       <c r="I27" s="66"/>
       <c r="J27" s="67">
         <f t="shared" si="2"/>
-        <v>-1470.22</v>
+        <v>-2940</v>
       </c>
       <c r="K27" s="67">
         <f t="shared" si="3"/>
@@ -4331,25 +4265,25 @@
       </c>
       <c r="M27" s="68">
         <f t="shared" si="5"/>
-        <v>380400</v>
+        <v>221900</v>
       </c>
       <c r="N27" s="69">
         <v>0</v>
       </c>
       <c r="O27" s="70">
         <f t="shared" si="0"/>
-        <v>378930.22</v>
+        <v>218960.22</v>
       </c>
       <c r="P27" s="71">
         <f t="shared" si="1"/>
-        <v>390298.22</v>
+        <v>225529.22</v>
       </c>
       <c r="Q27" s="41">
         <f t="shared" si="6"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
@@ -4360,18 +4294,18 @@
         <v>73</v>
       </c>
       <c r="D28" s="57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E28" s="58"/>
       <c r="F28" s="63">
         <v>4.66</v>
       </c>
       <c r="G28" s="64">
-        <v>486837.23</v>
+        <v>559200.23</v>
       </c>
       <c r="H28" s="65">
-        <f>G28</f>
-        <v>486837.23</v>
+        <f>486837.23+72363</f>
+        <v>559200.23</v>
       </c>
       <c r="I28" s="66"/>
       <c r="J28" s="67">
@@ -4388,25 +4322,25 @@
       </c>
       <c r="M28" s="68">
         <f t="shared" si="5"/>
-        <v>559200</v>
+        <v>326200</v>
       </c>
       <c r="N28" s="69">
         <v>0</v>
       </c>
       <c r="O28" s="70">
         <f t="shared" si="0"/>
-        <v>559200.23</v>
+        <v>326200.23</v>
       </c>
       <c r="P28" s="71">
         <f t="shared" si="1"/>
-        <v>575976.23</v>
+        <v>335986.23</v>
       </c>
       <c r="Q28" s="41">
         <f t="shared" si="6"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
@@ -4417,7 +4351,7 @@
         <v>74</v>
       </c>
       <c r="D29" s="57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E29" s="58"/>
       <c r="F29" s="63">
@@ -4445,25 +4379,25 @@
       </c>
       <c r="M29" s="68">
         <f t="shared" si="5"/>
-        <v>385199.99999999994</v>
+        <v>224699.99999999997</v>
       </c>
       <c r="N29" s="69">
         <v>0</v>
       </c>
       <c r="O29" s="70">
         <f t="shared" si="0"/>
-        <v>385200.24</v>
+        <v>224700.24</v>
       </c>
       <c r="P29" s="71">
         <f t="shared" si="1"/>
-        <v>396756.24</v>
+        <v>231441.24</v>
       </c>
       <c r="Q29" s="41">
         <f t="shared" si="6"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
@@ -4474,26 +4408,27 @@
         <v>75</v>
       </c>
       <c r="D30" s="57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E30" s="57"/>
       <c r="F30" s="63">
         <v>4.6900000000000004</v>
       </c>
       <c r="G30" s="64">
-        <v>562800.25</v>
-      </c>
-      <c r="H30" s="65">
-        <v>0</v>
+        <v>1142203.25</v>
+      </c>
+      <c r="H30" s="66">
+        <f>613669.25+562800</f>
+        <v>1176469.25</v>
       </c>
       <c r="I30" s="66"/>
       <c r="J30" s="67">
         <f t="shared" si="2"/>
-        <v>562800.25</v>
+        <v>-34266</v>
       </c>
       <c r="K30" s="67">
         <f t="shared" si="3"/>
-        <v>16602.607375</v>
+        <v>0</v>
       </c>
       <c r="L30" s="68">
         <f t="shared" si="4"/>
@@ -4501,25 +4436,28 @@
       </c>
       <c r="M30" s="68">
         <f t="shared" si="5"/>
-        <v>562800</v>
+        <v>328300.00000000006</v>
       </c>
       <c r="N30" s="69">
         <v>0</v>
       </c>
       <c r="O30" s="70">
         <f t="shared" si="0"/>
-        <v>1142203.25</v>
+        <v>294034.25</v>
       </c>
       <c r="P30" s="71">
         <f t="shared" si="1"/>
-        <v>1176469.25</v>
+        <v>302855.25</v>
       </c>
       <c r="Q30" s="41">
         <f t="shared" si="6"/>
         <v>0.25000000000000006</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R30" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
@@ -4530,23 +4468,22 @@
         <v>76</v>
       </c>
       <c r="D31" s="57" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E31" s="57"/>
       <c r="F31" s="63">
         <v>3.02</v>
       </c>
       <c r="G31" s="64">
-        <v>362399.26</v>
+        <v>362400.26</v>
       </c>
       <c r="H31" s="65">
-        <f>G31</f>
-        <v>362399.26</v>
+        <v>373272.26</v>
       </c>
       <c r="I31" s="66"/>
       <c r="J31" s="67">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-10872</v>
       </c>
       <c r="K31" s="67">
         <f t="shared" si="3"/>
@@ -4558,29 +4495,29 @@
       </c>
       <c r="M31" s="68">
         <f t="shared" si="5"/>
-        <v>362400</v>
+        <v>211400</v>
       </c>
       <c r="N31" s="69">
         <v>0</v>
       </c>
       <c r="O31" s="70">
         <f t="shared" si="0"/>
-        <v>362400.26</v>
+        <v>200528.26</v>
       </c>
       <c r="P31" s="71">
         <f t="shared" si="1"/>
-        <v>373272.26</v>
-      </c>
-      <c r="Q31" s="131">
+        <v>206544.26</v>
+      </c>
+      <c r="Q31" s="127">
         <f t="shared" si="6"/>
         <v>0.26000000000000006</v>
       </c>
-      <c r="R31" s="113"/>
+      <c r="R31" s="112"/>
       <c r="S31" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>27</v>
       </c>
@@ -4588,10 +4525,10 @@
         <v>27</v>
       </c>
       <c r="C32" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="57" t="s">
         <v>121</v>
-      </c>
-      <c r="D32" s="57" t="s">
-        <v>122</v>
       </c>
       <c r="E32" s="58"/>
       <c r="F32" s="63">
@@ -4601,17 +4538,16 @@
         <v>19200.27</v>
       </c>
       <c r="H32" s="65">
-        <f>G32</f>
-        <v>19200.27</v>
+        <v>12200.27</v>
       </c>
       <c r="I32" s="66"/>
       <c r="J32" s="67">
         <f>G32-H32</f>
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="K32" s="67">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>206.5</v>
       </c>
       <c r="L32" s="68">
         <f t="shared" si="4"/>
@@ -4619,25 +4555,25 @@
       </c>
       <c r="M32" s="68">
         <f>O$2*F32%</f>
-        <v>19200</v>
+        <v>11200</v>
       </c>
       <c r="N32" s="69">
         <v>0</v>
       </c>
       <c r="O32" s="70">
         <f t="shared" si="0"/>
-        <v>19200.27</v>
+        <v>18407.27</v>
       </c>
       <c r="P32" s="71">
         <f t="shared" si="1"/>
-        <v>19776.27</v>
+        <v>18959.27</v>
       </c>
       <c r="Q32" s="41">
         <f t="shared" si="6"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
@@ -4683,7 +4619,7 @@
       </c>
       <c r="Q33" s="41"/>
     </row>
-    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="77"/>
       <c r="C34" s="78"/>
       <c r="D34" s="79"/>
@@ -4694,11 +4630,11 @@
       </c>
       <c r="G34" s="47">
         <f>SUM(G6:G33)</f>
-        <v>13354658.339999998</v>
+        <v>15747408.76</v>
       </c>
       <c r="H34" s="55">
         <f>SUM(H6:H33)</f>
-        <v>9758198.1199999992</v>
+        <v>13720738.269999998</v>
       </c>
       <c r="I34" s="55">
         <f t="shared" ref="I34" si="10">SUM(I6:I33)</f>
@@ -4712,7 +4648,7 @@
       </c>
       <c r="M34" s="55">
         <f>SUM(M6:M33)</f>
-        <v>12000000</v>
+        <v>7000000</v>
       </c>
       <c r="N34" s="55">
         <f>SUM(N6:N33)</f>
@@ -4720,101 +4656,101 @@
       </c>
       <c r="O34" s="81">
         <f>SUM(O6:O32)</f>
-        <v>15725430.779999999</v>
+        <v>9106173.7799999993</v>
       </c>
       <c r="P34" s="81">
         <f>SUM(P6:P32)</f>
-        <v>16197192.779999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9379357.7799999993</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="45"/>
       <c r="E35" s="45"/>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D37" s="152"/>
-      <c r="E37" s="152"/>
-      <c r="F37" s="152"/>
-      <c r="G37" s="152"/>
-      <c r="H37" s="152"/>
-      <c r="I37" s="152"/>
-      <c r="J37" s="152"/>
-      <c r="K37" s="152"/>
-      <c r="L37" s="152"/>
-      <c r="M37" s="152"/>
-      <c r="N37" s="152"/>
-      <c r="O37" s="152"/>
-    </row>
-    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="152"/>
-      <c r="E38" s="152"/>
-      <c r="F38" s="152"/>
-      <c r="G38" s="152"/>
-      <c r="H38" s="152"/>
-      <c r="I38" s="152"/>
-      <c r="J38" s="152"/>
-      <c r="K38" s="152"/>
-      <c r="L38" s="152"/>
-      <c r="M38" s="152"/>
-      <c r="N38" s="152"/>
-      <c r="O38" s="152"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="152"/>
-      <c r="E39" s="152"/>
-      <c r="F39" s="152"/>
-      <c r="G39" s="152"/>
-      <c r="H39" s="152"/>
-      <c r="I39" s="152"/>
-      <c r="J39" s="152"/>
-      <c r="K39" s="152"/>
-      <c r="L39" s="152"/>
-      <c r="M39" s="152"/>
-      <c r="N39" s="152"/>
-      <c r="O39" s="152"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="152"/>
-      <c r="E40" s="152"/>
-      <c r="F40" s="152"/>
-      <c r="G40" s="152"/>
-      <c r="H40" s="152"/>
-      <c r="I40" s="152"/>
-      <c r="J40" s="152"/>
-      <c r="K40" s="152"/>
-      <c r="L40" s="152"/>
-      <c r="M40" s="152"/>
-      <c r="N40" s="152"/>
-      <c r="O40" s="152"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="152"/>
-      <c r="E41" s="152"/>
-      <c r="F41" s="152"/>
-      <c r="G41" s="152"/>
-      <c r="H41" s="152"/>
-      <c r="I41" s="152"/>
-      <c r="J41" s="152"/>
-      <c r="K41" s="152"/>
-      <c r="L41" s="152"/>
-      <c r="M41" s="152"/>
-      <c r="N41" s="152"/>
-      <c r="O41" s="152"/>
-    </row>
-    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="152"/>
-      <c r="E42" s="152"/>
-      <c r="F42" s="152"/>
-      <c r="G42" s="152"/>
-      <c r="H42" s="152"/>
-      <c r="I42" s="152"/>
-      <c r="J42" s="152"/>
-      <c r="K42" s="152"/>
-      <c r="L42" s="152"/>
-      <c r="M42" s="152"/>
-      <c r="N42" s="152"/>
-      <c r="O42" s="152"/>
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D37" s="147"/>
+      <c r="E37" s="147"/>
+      <c r="F37" s="147"/>
+      <c r="G37" s="147"/>
+      <c r="H37" s="147"/>
+      <c r="I37" s="147"/>
+      <c r="J37" s="147"/>
+      <c r="K37" s="147"/>
+      <c r="L37" s="147"/>
+      <c r="M37" s="147"/>
+      <c r="N37" s="147"/>
+      <c r="O37" s="147"/>
+    </row>
+    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D38" s="147"/>
+      <c r="E38" s="147"/>
+      <c r="F38" s="147"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="147"/>
+      <c r="I38" s="147"/>
+      <c r="J38" s="147"/>
+      <c r="K38" s="147"/>
+      <c r="L38" s="147"/>
+      <c r="M38" s="147"/>
+      <c r="N38" s="147"/>
+      <c r="O38" s="147"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="147"/>
+      <c r="E39" s="147"/>
+      <c r="F39" s="147"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="147"/>
+      <c r="J39" s="147"/>
+      <c r="K39" s="147"/>
+      <c r="L39" s="147"/>
+      <c r="M39" s="147"/>
+      <c r="N39" s="147"/>
+      <c r="O39" s="147"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="147"/>
+      <c r="E40" s="147"/>
+      <c r="F40" s="147"/>
+      <c r="G40" s="147"/>
+      <c r="H40" s="147"/>
+      <c r="I40" s="147"/>
+      <c r="J40" s="147"/>
+      <c r="K40" s="147"/>
+      <c r="L40" s="147"/>
+      <c r="M40" s="147"/>
+      <c r="N40" s="147"/>
+      <c r="O40" s="147"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D41" s="147"/>
+      <c r="E41" s="147"/>
+      <c r="F41" s="147"/>
+      <c r="G41" s="147"/>
+      <c r="H41" s="147"/>
+      <c r="I41" s="147"/>
+      <c r="J41" s="147"/>
+      <c r="K41" s="147"/>
+      <c r="L41" s="147"/>
+      <c r="M41" s="147"/>
+      <c r="N41" s="147"/>
+      <c r="O41" s="147"/>
+    </row>
+    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D42" s="147"/>
+      <c r="E42" s="147"/>
+      <c r="F42" s="147"/>
+      <c r="G42" s="147"/>
+      <c r="H42" s="147"/>
+      <c r="I42" s="147"/>
+      <c r="J42" s="147"/>
+      <c r="K42" s="147"/>
+      <c r="L42" s="147"/>
+      <c r="M42" s="147"/>
+      <c r="N42" s="147"/>
+      <c r="O42" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="17">

--- a/colombres/Agosto/AGOSTO COLOMBRES 360.xlsx
+++ b/colombres/Agosto/AGOSTO COLOMBRES 360.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A19E44-A3FE-4C51-AD56-A87D72EA48AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FFEBA3-46FA-42E6-9EEE-19638DB37B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -547,7 +547,7 @@
     <t>MES QUE VIENE PENDIENTE UNA FACTURA DE TAUGE Y OTRA FACTURA QUE DEBEMOS EDITAR DE 4600</t>
   </si>
   <si>
-    <t>Hay que sacarle $16,000 de punitorios debe quedar sin deuda</t>
+    <t>Hay que sacarle $16,000 de punitorios debe quedar sin deuda - Pagando $319,139</t>
   </si>
 </sst>
 </file>
@@ -1392,6 +1392,49 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1401,47 +1444,47 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1455,49 +1498,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1890,68 +1890,68 @@
       <c r="D3" s="125"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="153" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="163"/>
+      <c r="B4" s="153"/>
       <c r="C4" s="126"/>
       <c r="D4" s="126"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="163"/>
-      <c r="B5" s="163"/>
+      <c r="A5" s="153"/>
+      <c r="B5" s="153"/>
       <c r="C5" s="126"/>
       <c r="D5" s="126"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="163"/>
-      <c r="B6" s="163"/>
+      <c r="A6" s="153"/>
+      <c r="B6" s="153"/>
       <c r="C6" s="126"/>
       <c r="D6" s="126"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="163"/>
-      <c r="B7" s="163"/>
+      <c r="A7" s="153"/>
+      <c r="B7" s="153"/>
       <c r="C7" s="126"/>
       <c r="D7" s="126"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="150" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="162"/>
+      <c r="B10" s="150"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="162"/>
+      <c r="B11" s="150"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="152" t="s">
+      <c r="A14" s="154" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="152"/>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
+      <c r="D14" s="154"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="152"/>
-      <c r="B15" s="152"/>
-      <c r="C15" s="152"/>
-      <c r="D15" s="152"/>
+      <c r="A15" s="154"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="152"/>
-      <c r="B16" s="152"/>
-      <c r="C16" s="152"/>
-      <c r="D16" s="152"/>
+      <c r="A16" s="154"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="152"/>
-      <c r="B17" s="152"/>
-      <c r="C17" s="152"/>
-      <c r="D17" s="152"/>
+      <c r="A17" s="154"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="154"/>
+      <c r="D17" s="154"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2024,10 +2024,10 @@
         <v>959820.72999999986</v>
       </c>
       <c r="D27" s="85"/>
-      <c r="F27" s="160" t="s">
+      <c r="F27" s="148" t="s">
         <v>167</v>
       </c>
-      <c r="G27" s="161"/>
+      <c r="G27" s="149"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="131" t="s">
@@ -2040,8 +2040,8 @@
         <v>886097.5</v>
       </c>
       <c r="D28" s="84"/>
-      <c r="F28" s="160"/>
-      <c r="G28" s="161"/>
+      <c r="F28" s="148"/>
+      <c r="G28" s="149"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
@@ -2231,10 +2231,10 @@
       <c r="D45" s="61"/>
     </row>
     <row r="46" spans="1:7" s="35" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="150" t="s">
+      <c r="A46" s="151" t="s">
         <v>129</v>
       </c>
-      <c r="B46" s="151"/>
+      <c r="B46" s="152"/>
       <c r="C46" s="139">
         <v>175052</v>
       </c>
@@ -2243,10 +2243,10 @@
       </c>
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="150" t="s">
+      <c r="A47" s="151" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="151"/>
+      <c r="B47" s="152"/>
       <c r="C47" s="140">
         <v>4203</v>
       </c>
@@ -2388,10 +2388,10 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="150" t="s">
+      <c r="A59" s="151" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="151"/>
+      <c r="B59" s="152"/>
       <c r="C59" s="110">
         <v>308630</v>
       </c>
@@ -2400,10 +2400,10 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="158" t="s">
+      <c r="A60" s="160" t="s">
         <v>155</v>
       </c>
-      <c r="B60" s="159"/>
+      <c r="B60" s="161"/>
       <c r="C60" s="110">
         <v>158501</v>
       </c>
@@ -2451,10 +2451,10 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="156" t="s">
+      <c r="A65" s="158" t="s">
         <v>154</v>
       </c>
-      <c r="B65" s="157"/>
+      <c r="B65" s="159"/>
       <c r="C65" s="31">
         <v>99268</v>
       </c>
@@ -2519,11 +2519,11 @@
       <c r="D71" s="100"/>
     </row>
     <row r="72" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="153" t="s">
+      <c r="A72" s="155" t="s">
         <v>162</v>
       </c>
-      <c r="B72" s="154"/>
-      <c r="C72" s="155"/>
+      <c r="B72" s="156"/>
+      <c r="C72" s="157"/>
       <c r="D72" s="101"/>
     </row>
     <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2562,14 +2562,14 @@
       <c r="D77" s="107"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="150"/>
-      <c r="B78" s="151"/>
+      <c r="A78" s="151"/>
+      <c r="B78" s="152"/>
       <c r="C78" s="94"/>
       <c r="D78" s="92"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="150"/>
-      <c r="B79" s="151"/>
+      <c r="A79" s="151"/>
+      <c r="B79" s="152"/>
       <c r="C79" s="94"/>
       <c r="D79" s="92"/>
     </row>
@@ -2651,22 +2651,22 @@
     <row r="92" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="149"/>
-      <c r="B94" s="149"/>
-      <c r="C94" s="149"/>
-      <c r="D94" s="149"/>
+      <c r="A94" s="164"/>
+      <c r="B94" s="164"/>
+      <c r="C94" s="164"/>
+      <c r="D94" s="164"/>
     </row>
     <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="149"/>
-      <c r="B95" s="149"/>
-      <c r="C95" s="149"/>
-      <c r="D95" s="149"/>
+      <c r="A95" s="164"/>
+      <c r="B95" s="164"/>
+      <c r="C95" s="164"/>
+      <c r="D95" s="164"/>
     </row>
     <row r="96" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="149"/>
-      <c r="B96" s="149"/>
-      <c r="C96" s="149"/>
-      <c r="D96" s="149"/>
+      <c r="A96" s="164"/>
+      <c r="B96" s="164"/>
+      <c r="C96" s="164"/>
+      <c r="D96" s="164"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
@@ -2773,14 +2773,14 @@
       <c r="C110" s="41"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="148" t="s">
+      <c r="A112" s="163" t="s">
         <v>78</v>
       </c>
-      <c r="B112" s="148"/>
+      <c r="B112" s="163"/>
     </row>
     <row r="113" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="148"/>
-      <c r="B113" s="148"/>
+      <c r="A113" s="163"/>
+      <c r="B113" s="163"/>
     </row>
     <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="108"/>
@@ -2819,46 +2819,46 @@
       <c r="L121" s="8"/>
     </row>
     <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="147"/>
-      <c r="B122" s="147"/>
-      <c r="C122" s="147"/>
-      <c r="D122" s="147"/>
+      <c r="A122" s="162"/>
+      <c r="B122" s="162"/>
+      <c r="C122" s="162"/>
+      <c r="D122" s="162"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="147"/>
-      <c r="B123" s="147"/>
-      <c r="C123" s="147"/>
-      <c r="D123" s="147"/>
+      <c r="A123" s="162"/>
+      <c r="B123" s="162"/>
+      <c r="C123" s="162"/>
+      <c r="D123" s="162"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="147"/>
-      <c r="B124" s="147"/>
-      <c r="C124" s="147"/>
-      <c r="D124" s="147"/>
+      <c r="A124" s="162"/>
+      <c r="B124" s="162"/>
+      <c r="C124" s="162"/>
+      <c r="D124" s="162"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="147"/>
-      <c r="B125" s="147"/>
-      <c r="C125" s="147"/>
-      <c r="D125" s="147"/>
+      <c r="A125" s="162"/>
+      <c r="B125" s="162"/>
+      <c r="C125" s="162"/>
+      <c r="D125" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A122:D125"/>
+    <mergeCell ref="A112:B113"/>
+    <mergeCell ref="A94:D96"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="F27:G28"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A122:D125"/>
-    <mergeCell ref="A112:B113"/>
-    <mergeCell ref="A94:D96"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A78:B78"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2894,18 +2894,18 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="170" t="s">
+      <c r="B1" s="165" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="B2" s="165"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="165"/>
+      <c r="J2" s="165"/>
+      <c r="K2" s="165"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -2937,16 +2937,16 @@
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="171"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="171"/>
-      <c r="G3" s="171"/>
-      <c r="H3" s="171"/>
-      <c r="I3" s="171"/>
-      <c r="J3" s="171"/>
-      <c r="K3" s="171"/>
+      <c r="B3" s="166"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="166"/>
+      <c r="E3" s="166"/>
+      <c r="F3" s="166"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="166"/>
+      <c r="I3" s="166"/>
+      <c r="J3" s="166"/>
+      <c r="K3" s="166"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -2956,76 +2956,76 @@
       <c r="P3" s="53"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="164" t="s">
+      <c r="A4" s="179" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="166" t="s">
+      <c r="B4" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="168" t="s">
+      <c r="C4" s="169" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="168" t="s">
+      <c r="D4" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="168" t="s">
+      <c r="E4" s="169" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="168" t="s">
+      <c r="F4" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="168" t="s">
+      <c r="G4" s="169" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="168" t="s">
+      <c r="H4" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="168" t="s">
+      <c r="I4" s="169" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="177" t="s">
+      <c r="J4" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="175" t="s">
+      <c r="K4" s="171" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="175" t="s">
+      <c r="L4" s="171" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="175" t="s">
+      <c r="M4" s="171" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="180" t="s">
+      <c r="N4" s="177" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="172" t="s">
+      <c r="P4" s="167" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="41"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="165"/>
-      <c r="B5" s="167"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="169"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="169"/>
-      <c r="G5" s="169"/>
-      <c r="H5" s="169"/>
-      <c r="I5" s="174"/>
-      <c r="J5" s="178"/>
-      <c r="K5" s="176"/>
-      <c r="L5" s="179"/>
-      <c r="M5" s="176"/>
-      <c r="N5" s="181"/>
+      <c r="A5" s="180"/>
+      <c r="B5" s="182"/>
+      <c r="C5" s="173"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="170"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
+      <c r="H5" s="173"/>
+      <c r="I5" s="170"/>
+      <c r="J5" s="175"/>
+      <c r="K5" s="172"/>
+      <c r="L5" s="176"/>
+      <c r="M5" s="172"/>
+      <c r="N5" s="178"/>
       <c r="O5" s="54" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/09</v>
       </c>
-      <c r="P5" s="173"/>
+      <c r="P5" s="168"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3423,6 +3423,7 @@
         <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
+      <c r="R12" s="138"/>
       <c r="S12" s="134"/>
     </row>
     <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3506,7 +3507,7 @@
         <v>1093000</v>
       </c>
       <c r="I14" s="66"/>
-      <c r="J14" s="182">
+      <c r="J14" s="147">
         <f t="shared" si="2"/>
         <v>16005.090000000084</v>
       </c>
@@ -4669,91 +4670,96 @@
     </row>
     <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="147"/>
-      <c r="E37" s="147"/>
-      <c r="F37" s="147"/>
-      <c r="G37" s="147"/>
-      <c r="H37" s="147"/>
-      <c r="I37" s="147"/>
-      <c r="J37" s="147"/>
-      <c r="K37" s="147"/>
-      <c r="L37" s="147"/>
-      <c r="M37" s="147"/>
-      <c r="N37" s="147"/>
-      <c r="O37" s="147"/>
+      <c r="D37" s="162"/>
+      <c r="E37" s="162"/>
+      <c r="F37" s="162"/>
+      <c r="G37" s="162"/>
+      <c r="H37" s="162"/>
+      <c r="I37" s="162"/>
+      <c r="J37" s="162"/>
+      <c r="K37" s="162"/>
+      <c r="L37" s="162"/>
+      <c r="M37" s="162"/>
+      <c r="N37" s="162"/>
+      <c r="O37" s="162"/>
     </row>
     <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="147"/>
-      <c r="E38" s="147"/>
-      <c r="F38" s="147"/>
-      <c r="G38" s="147"/>
-      <c r="H38" s="147"/>
-      <c r="I38" s="147"/>
-      <c r="J38" s="147"/>
-      <c r="K38" s="147"/>
-      <c r="L38" s="147"/>
-      <c r="M38" s="147"/>
-      <c r="N38" s="147"/>
-      <c r="O38" s="147"/>
+      <c r="D38" s="162"/>
+      <c r="E38" s="162"/>
+      <c r="F38" s="162"/>
+      <c r="G38" s="162"/>
+      <c r="H38" s="162"/>
+      <c r="I38" s="162"/>
+      <c r="J38" s="162"/>
+      <c r="K38" s="162"/>
+      <c r="L38" s="162"/>
+      <c r="M38" s="162"/>
+      <c r="N38" s="162"/>
+      <c r="O38" s="162"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="147"/>
-      <c r="E39" s="147"/>
-      <c r="F39" s="147"/>
-      <c r="G39" s="147"/>
-      <c r="H39" s="147"/>
-      <c r="I39" s="147"/>
-      <c r="J39" s="147"/>
-      <c r="K39" s="147"/>
-      <c r="L39" s="147"/>
-      <c r="M39" s="147"/>
-      <c r="N39" s="147"/>
-      <c r="O39" s="147"/>
+      <c r="D39" s="162"/>
+      <c r="E39" s="162"/>
+      <c r="F39" s="162"/>
+      <c r="G39" s="162"/>
+      <c r="H39" s="162"/>
+      <c r="I39" s="162"/>
+      <c r="J39" s="162"/>
+      <c r="K39" s="162"/>
+      <c r="L39" s="162"/>
+      <c r="M39" s="162"/>
+      <c r="N39" s="162"/>
+      <c r="O39" s="162"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="147"/>
-      <c r="E40" s="147"/>
-      <c r="F40" s="147"/>
-      <c r="G40" s="147"/>
-      <c r="H40" s="147"/>
-      <c r="I40" s="147"/>
-      <c r="J40" s="147"/>
-      <c r="K40" s="147"/>
-      <c r="L40" s="147"/>
-      <c r="M40" s="147"/>
-      <c r="N40" s="147"/>
-      <c r="O40" s="147"/>
+      <c r="D40" s="162"/>
+      <c r="E40" s="162"/>
+      <c r="F40" s="162"/>
+      <c r="G40" s="162"/>
+      <c r="H40" s="162"/>
+      <c r="I40" s="162"/>
+      <c r="J40" s="162"/>
+      <c r="K40" s="162"/>
+      <c r="L40" s="162"/>
+      <c r="M40" s="162"/>
+      <c r="N40" s="162"/>
+      <c r="O40" s="162"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="147"/>
-      <c r="E41" s="147"/>
-      <c r="F41" s="147"/>
-      <c r="G41" s="147"/>
-      <c r="H41" s="147"/>
-      <c r="I41" s="147"/>
-      <c r="J41" s="147"/>
-      <c r="K41" s="147"/>
-      <c r="L41" s="147"/>
-      <c r="M41" s="147"/>
-      <c r="N41" s="147"/>
-      <c r="O41" s="147"/>
+      <c r="D41" s="162"/>
+      <c r="E41" s="162"/>
+      <c r="F41" s="162"/>
+      <c r="G41" s="162"/>
+      <c r="H41" s="162"/>
+      <c r="I41" s="162"/>
+      <c r="J41" s="162"/>
+      <c r="K41" s="162"/>
+      <c r="L41" s="162"/>
+      <c r="M41" s="162"/>
+      <c r="N41" s="162"/>
+      <c r="O41" s="162"/>
     </row>
     <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="147"/>
-      <c r="E42" s="147"/>
-      <c r="F42" s="147"/>
-      <c r="G42" s="147"/>
-      <c r="H42" s="147"/>
-      <c r="I42" s="147"/>
-      <c r="J42" s="147"/>
-      <c r="K42" s="147"/>
-      <c r="L42" s="147"/>
-      <c r="M42" s="147"/>
-      <c r="N42" s="147"/>
-      <c r="O42" s="147"/>
+      <c r="D42" s="162"/>
+      <c r="E42" s="162"/>
+      <c r="F42" s="162"/>
+      <c r="G42" s="162"/>
+      <c r="H42" s="162"/>
+      <c r="I42" s="162"/>
+      <c r="J42" s="162"/>
+      <c r="K42" s="162"/>
+      <c r="L42" s="162"/>
+      <c r="M42" s="162"/>
+      <c r="N42" s="162"/>
+      <c r="O42" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4766,11 +4772,6 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/colombres/Agosto/AGOSTO COLOMBRES 360.xlsx
+++ b/colombres/Agosto/AGOSTO COLOMBRES 360.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FFEBA3-46FA-42E6-9EEE-19638DB37B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517FEE79-3C32-463B-BD15-7B46B95F2F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -555,12 +555,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -1181,8 +1181,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1192,14 +1192,14 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1207,7 +1207,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1215,44 +1215,44 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="19" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1266,67 +1266,67 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
@@ -1336,13 +1336,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1356,8 +1356,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1368,16 +1368,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1388,11 +1388,50 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="25" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="25" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1402,47 +1441,26 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1456,9 +1474,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1468,9 +1483,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1485,18 +1497,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1890,68 +1890,68 @@
       <c r="D3" s="125"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="153" t="s">
+      <c r="A4" s="164" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="153"/>
+      <c r="B4" s="164"/>
       <c r="C4" s="126"/>
       <c r="D4" s="126"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="153"/>
-      <c r="B5" s="153"/>
+      <c r="A5" s="164"/>
+      <c r="B5" s="164"/>
       <c r="C5" s="126"/>
       <c r="D5" s="126"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="153"/>
-      <c r="B6" s="153"/>
+      <c r="A6" s="164"/>
+      <c r="B6" s="164"/>
       <c r="C6" s="126"/>
       <c r="D6" s="126"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="153"/>
-      <c r="B7" s="153"/>
+      <c r="A7" s="164"/>
+      <c r="B7" s="164"/>
       <c r="C7" s="126"/>
       <c r="D7" s="126"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="150" t="s">
+      <c r="B9" s="163" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="150"/>
+      <c r="B10" s="163"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="150"/>
+      <c r="B11" s="163"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="154" t="s">
+      <c r="A14" s="153" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="154"/>
-      <c r="C14" s="154"/>
-      <c r="D14" s="154"/>
+      <c r="B14" s="153"/>
+      <c r="C14" s="153"/>
+      <c r="D14" s="153"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="154"/>
-      <c r="B15" s="154"/>
-      <c r="C15" s="154"/>
-      <c r="D15" s="154"/>
+      <c r="A15" s="153"/>
+      <c r="B15" s="153"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="153"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="154"/>
-      <c r="B16" s="154"/>
-      <c r="C16" s="154"/>
-      <c r="D16" s="154"/>
+      <c r="A16" s="153"/>
+      <c r="B16" s="153"/>
+      <c r="C16" s="153"/>
+      <c r="D16" s="153"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="154"/>
-      <c r="B17" s="154"/>
-      <c r="C17" s="154"/>
-      <c r="D17" s="154"/>
+      <c r="A17" s="153"/>
+      <c r="B17" s="153"/>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2024,10 +2024,10 @@
         <v>959820.72999999986</v>
       </c>
       <c r="D27" s="85"/>
-      <c r="F27" s="148" t="s">
+      <c r="F27" s="161" t="s">
         <v>167</v>
       </c>
-      <c r="G27" s="149"/>
+      <c r="G27" s="162"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="131" t="s">
@@ -2040,8 +2040,8 @@
         <v>886097.5</v>
       </c>
       <c r="D28" s="84"/>
-      <c r="F28" s="148"/>
-      <c r="G28" s="149"/>
+      <c r="F28" s="161"/>
+      <c r="G28" s="162"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
@@ -2400,10 +2400,10 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="160" t="s">
+      <c r="A60" s="159" t="s">
         <v>155</v>
       </c>
-      <c r="B60" s="161"/>
+      <c r="B60" s="160"/>
       <c r="C60" s="110">
         <v>158501</v>
       </c>
@@ -2451,10 +2451,10 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="158" t="s">
+      <c r="A65" s="157" t="s">
         <v>154</v>
       </c>
-      <c r="B65" s="159"/>
+      <c r="B65" s="158"/>
       <c r="C65" s="31">
         <v>99268</v>
       </c>
@@ -2519,11 +2519,11 @@
       <c r="D71" s="100"/>
     </row>
     <row r="72" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="155" t="s">
+      <c r="A72" s="154" t="s">
         <v>162</v>
       </c>
-      <c r="B72" s="156"/>
-      <c r="C72" s="157"/>
+      <c r="B72" s="155"/>
+      <c r="C72" s="156"/>
       <c r="D72" s="101"/>
     </row>
     <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2651,22 +2651,22 @@
     <row r="92" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="164"/>
-      <c r="B94" s="164"/>
-      <c r="C94" s="164"/>
-      <c r="D94" s="164"/>
+      <c r="A94" s="150"/>
+      <c r="B94" s="150"/>
+      <c r="C94" s="150"/>
+      <c r="D94" s="150"/>
     </row>
     <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="164"/>
-      <c r="B95" s="164"/>
-      <c r="C95" s="164"/>
-      <c r="D95" s="164"/>
+      <c r="A95" s="150"/>
+      <c r="B95" s="150"/>
+      <c r="C95" s="150"/>
+      <c r="D95" s="150"/>
     </row>
     <row r="96" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="164"/>
-      <c r="B96" s="164"/>
-      <c r="C96" s="164"/>
-      <c r="D96" s="164"/>
+      <c r="A96" s="150"/>
+      <c r="B96" s="150"/>
+      <c r="C96" s="150"/>
+      <c r="D96" s="150"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
@@ -2773,14 +2773,14 @@
       <c r="C110" s="41"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="163" t="s">
+      <c r="A112" s="149" t="s">
         <v>78</v>
       </c>
-      <c r="B112" s="163"/>
+      <c r="B112" s="149"/>
     </row>
     <row r="113" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="163"/>
-      <c r="B113" s="163"/>
+      <c r="A113" s="149"/>
+      <c r="B113" s="149"/>
     </row>
     <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="108"/>
@@ -2819,46 +2819,46 @@
       <c r="L121" s="8"/>
     </row>
     <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="162"/>
-      <c r="B122" s="162"/>
-      <c r="C122" s="162"/>
-      <c r="D122" s="162"/>
+      <c r="A122" s="148"/>
+      <c r="B122" s="148"/>
+      <c r="C122" s="148"/>
+      <c r="D122" s="148"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="162"/>
-      <c r="B123" s="162"/>
-      <c r="C123" s="162"/>
-      <c r="D123" s="162"/>
+      <c r="A123" s="148"/>
+      <c r="B123" s="148"/>
+      <c r="C123" s="148"/>
+      <c r="D123" s="148"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="162"/>
-      <c r="B124" s="162"/>
-      <c r="C124" s="162"/>
-      <c r="D124" s="162"/>
+      <c r="A124" s="148"/>
+      <c r="B124" s="148"/>
+      <c r="C124" s="148"/>
+      <c r="D124" s="148"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="162"/>
-      <c r="B125" s="162"/>
-      <c r="C125" s="162"/>
-      <c r="D125" s="162"/>
+      <c r="A125" s="148"/>
+      <c r="B125" s="148"/>
+      <c r="C125" s="148"/>
+      <c r="D125" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="F27:G28"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A4:B7"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A122:D125"/>
     <mergeCell ref="A112:B113"/>
     <mergeCell ref="A94:D96"/>
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="F27:G28"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A47:B47"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2894,18 +2894,18 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="165" t="s">
+      <c r="B1" s="171" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
-      <c r="G1" s="165"/>
-      <c r="H1" s="165"/>
-      <c r="I1" s="165"/>
-      <c r="J1" s="165"/>
-      <c r="K1" s="165"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="165"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="165"/>
-      <c r="J2" s="165"/>
-      <c r="K2" s="165"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -2937,16 +2937,16 @@
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="166"/>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="166"/>
-      <c r="I3" s="166"/>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="172"/>
+      <c r="I3" s="172"/>
+      <c r="J3" s="172"/>
+      <c r="K3" s="172"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -2956,10 +2956,10 @@
       <c r="P3" s="53"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="179" t="s">
+      <c r="A4" s="165" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="181" t="s">
+      <c r="B4" s="167" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="169" t="s">
@@ -2983,49 +2983,49 @@
       <c r="I4" s="169" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="174" t="s">
+      <c r="J4" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="171" t="s">
+      <c r="K4" s="176" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="171" t="s">
+      <c r="L4" s="176" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="171" t="s">
+      <c r="M4" s="176" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="177" t="s">
+      <c r="N4" s="181" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="167" t="s">
+      <c r="P4" s="173" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="41"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="180"/>
-      <c r="B5" s="182"/>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="170"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
-      <c r="I5" s="170"/>
-      <c r="J5" s="175"/>
-      <c r="K5" s="172"/>
-      <c r="L5" s="176"/>
-      <c r="M5" s="172"/>
-      <c r="N5" s="178"/>
+      <c r="A5" s="166"/>
+      <c r="B5" s="168"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="170"/>
+      <c r="H5" s="170"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="179"/>
+      <c r="K5" s="177"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="177"/>
+      <c r="N5" s="182"/>
       <c r="O5" s="54" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/09</v>
       </c>
-      <c r="P5" s="168"/>
+      <c r="P5" s="174"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -4670,96 +4670,91 @@
     </row>
     <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="162"/>
-      <c r="E37" s="162"/>
-      <c r="F37" s="162"/>
-      <c r="G37" s="162"/>
-      <c r="H37" s="162"/>
-      <c r="I37" s="162"/>
-      <c r="J37" s="162"/>
-      <c r="K37" s="162"/>
-      <c r="L37" s="162"/>
-      <c r="M37" s="162"/>
-      <c r="N37" s="162"/>
-      <c r="O37" s="162"/>
+      <c r="D37" s="148"/>
+      <c r="E37" s="148"/>
+      <c r="F37" s="148"/>
+      <c r="G37" s="148"/>
+      <c r="H37" s="148"/>
+      <c r="I37" s="148"/>
+      <c r="J37" s="148"/>
+      <c r="K37" s="148"/>
+      <c r="L37" s="148"/>
+      <c r="M37" s="148"/>
+      <c r="N37" s="148"/>
+      <c r="O37" s="148"/>
     </row>
     <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="162"/>
-      <c r="E38" s="162"/>
-      <c r="F38" s="162"/>
-      <c r="G38" s="162"/>
-      <c r="H38" s="162"/>
-      <c r="I38" s="162"/>
-      <c r="J38" s="162"/>
-      <c r="K38" s="162"/>
-      <c r="L38" s="162"/>
-      <c r="M38" s="162"/>
-      <c r="N38" s="162"/>
-      <c r="O38" s="162"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="148"/>
+      <c r="F38" s="148"/>
+      <c r="G38" s="148"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="148"/>
+      <c r="J38" s="148"/>
+      <c r="K38" s="148"/>
+      <c r="L38" s="148"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="148"/>
+      <c r="O38" s="148"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="162"/>
-      <c r="E39" s="162"/>
-      <c r="F39" s="162"/>
-      <c r="G39" s="162"/>
-      <c r="H39" s="162"/>
-      <c r="I39" s="162"/>
-      <c r="J39" s="162"/>
-      <c r="K39" s="162"/>
-      <c r="L39" s="162"/>
-      <c r="M39" s="162"/>
-      <c r="N39" s="162"/>
-      <c r="O39" s="162"/>
+      <c r="D39" s="148"/>
+      <c r="E39" s="148"/>
+      <c r="F39" s="148"/>
+      <c r="G39" s="148"/>
+      <c r="H39" s="148"/>
+      <c r="I39" s="148"/>
+      <c r="J39" s="148"/>
+      <c r="K39" s="148"/>
+      <c r="L39" s="148"/>
+      <c r="M39" s="148"/>
+      <c r="N39" s="148"/>
+      <c r="O39" s="148"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="162"/>
-      <c r="E40" s="162"/>
-      <c r="F40" s="162"/>
-      <c r="G40" s="162"/>
-      <c r="H40" s="162"/>
-      <c r="I40" s="162"/>
-      <c r="J40" s="162"/>
-      <c r="K40" s="162"/>
-      <c r="L40" s="162"/>
-      <c r="M40" s="162"/>
-      <c r="N40" s="162"/>
-      <c r="O40" s="162"/>
+      <c r="D40" s="148"/>
+      <c r="E40" s="148"/>
+      <c r="F40" s="148"/>
+      <c r="G40" s="148"/>
+      <c r="H40" s="148"/>
+      <c r="I40" s="148"/>
+      <c r="J40" s="148"/>
+      <c r="K40" s="148"/>
+      <c r="L40" s="148"/>
+      <c r="M40" s="148"/>
+      <c r="N40" s="148"/>
+      <c r="O40" s="148"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="162"/>
-      <c r="E41" s="162"/>
-      <c r="F41" s="162"/>
-      <c r="G41" s="162"/>
-      <c r="H41" s="162"/>
-      <c r="I41" s="162"/>
-      <c r="J41" s="162"/>
-      <c r="K41" s="162"/>
-      <c r="L41" s="162"/>
-      <c r="M41" s="162"/>
-      <c r="N41" s="162"/>
-      <c r="O41" s="162"/>
+      <c r="D41" s="148"/>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="148"/>
+      <c r="H41" s="148"/>
+      <c r="I41" s="148"/>
+      <c r="J41" s="148"/>
+      <c r="K41" s="148"/>
+      <c r="L41" s="148"/>
+      <c r="M41" s="148"/>
+      <c r="N41" s="148"/>
+      <c r="O41" s="148"/>
     </row>
     <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="162"/>
-      <c r="E42" s="162"/>
-      <c r="F42" s="162"/>
-      <c r="G42" s="162"/>
-      <c r="H42" s="162"/>
-      <c r="I42" s="162"/>
-      <c r="J42" s="162"/>
-      <c r="K42" s="162"/>
-      <c r="L42" s="162"/>
-      <c r="M42" s="162"/>
-      <c r="N42" s="162"/>
-      <c r="O42" s="162"/>
+      <c r="D42" s="148"/>
+      <c r="E42" s="148"/>
+      <c r="F42" s="148"/>
+      <c r="G42" s="148"/>
+      <c r="H42" s="148"/>
+      <c r="I42" s="148"/>
+      <c r="J42" s="148"/>
+      <c r="K42" s="148"/>
+      <c r="L42" s="148"/>
+      <c r="M42" s="148"/>
+      <c r="N42" s="148"/>
+      <c r="O42" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4772,6 +4767,11 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
